--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>607.5055950000001</v>
+        <v>607.505625</v>
       </c>
       <c r="H3" t="n">
         <v>835282</v>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>584.8229690000002</v>
+        <v>584.822999</v>
       </c>
       <c r="H4" t="n">
         <v>816275</v>
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>524.4741879999999</v>
+        <v>524.474118</v>
       </c>
       <c r="H5" t="n">
         <v>801530</v>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>452.7995879999997</v>
+        <v>452.799568</v>
       </c>
       <c r="H6" t="n">
         <v>801538</v>
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>449.8547350000002</v>
+        <v>449.854736</v>
       </c>
       <c r="H7" t="n">
         <v>818654</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>449.6804200000002</v>
+        <v>449.680421</v>
       </c>
       <c r="H8" t="n">
         <v>811470</v>
@@ -5824,16 +5824,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>811470</v>
+        <v>816275</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5841,17 +5841,17 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3393.143</v>
+        <v>3385.5386</v>
       </c>
       <c r="H102" t="n">
-        <v>3548.692</v>
+        <v>3600</v>
       </c>
       <c r="I102" t="n">
-        <v>155.549</v>
+        <v>214.461</v>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K102" t="b">
@@ -5869,16 +5869,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>891409</v>
+        <v>835282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5886,17 +5886,17 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3393.143</v>
+        <v>3385.5386</v>
       </c>
       <c r="H103" t="n">
-        <v>3447.7573</v>
+        <v>3600</v>
       </c>
       <c r="I103" t="n">
-        <v>54.614</v>
+        <v>214.461</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K103" t="b">
@@ -5914,16 +5914,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>818654</v>
+        <v>811470</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5931,17 +5931,17 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3447.7573</v>
+        <v>3393.143</v>
       </c>
       <c r="H104" t="n">
-        <v>3550.9062</v>
+        <v>3548.692</v>
       </c>
       <c r="I104" t="n">
-        <v>103.149</v>
+        <v>155.549</v>
       </c>
       <c r="J104" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K104" t="b">
@@ -5976,17 +5976,17 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3548.692</v>
+        <v>3393.143</v>
       </c>
       <c r="H105" t="n">
-        <v>3594.3313</v>
+        <v>3447.7573</v>
       </c>
       <c r="I105" t="n">
-        <v>45.639</v>
+        <v>54.614</v>
       </c>
       <c r="J105" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K105" t="b">
@@ -6004,16 +6004,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>816244</v>
+        <v>801530</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6021,17 +6021,17 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3550.9062</v>
+        <v>3393.143</v>
       </c>
       <c r="H106" t="n">
-        <v>3594.3313</v>
+        <v>3600</v>
       </c>
       <c r="I106" t="n">
-        <v>43.425</v>
+        <v>206.857</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="K106" t="b">
@@ -6049,16 +6049,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>816275</v>
+        <v>801538</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6066,19 +6066,21 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3385.5386</v>
-      </c>
-      <c r="H107" t="inlineStr"/>
+        <v>3447.7573</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3600</v>
+      </c>
       <c r="I107" t="n">
-        <v>214.461</v>
+        <v>152.243</v>
       </c>
       <c r="J107" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -6092,16 +6094,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>835282</v>
+        <v>818654</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6109,19 +6111,21 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3385.5386</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>3447.7573</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3550.9062</v>
+      </c>
       <c r="I108" t="n">
-        <v>214.461</v>
+        <v>103.149</v>
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6135,16 +6139,16 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>801530</v>
+        <v>891409</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6152,19 +6156,21 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3393.143</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>3548.692</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3594.3313</v>
+      </c>
       <c r="I109" t="n">
-        <v>206.857</v>
+        <v>45.639</v>
       </c>
       <c r="J109" s="1" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -6178,16 +6184,16 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>801538</v>
+        <v>816244</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6195,19 +6201,21 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3447.7573</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>3550.9062</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3594.3313</v>
+      </c>
       <c r="I110" t="n">
-        <v>152.243</v>
+        <v>43.425</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="K110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -6221,16 +6229,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>818654</v>
+        <v>811470</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6240,7 +6248,9 @@
       <c r="G111" t="n">
         <v>3594.3313</v>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>3600</v>
+      </c>
       <c r="I111" t="n">
         <v>5.669</v>
       </c>
@@ -6250,7 +6260,7 @@
         </is>
       </c>
       <c r="K111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -6264,16 +6274,16 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>811470</v>
+        <v>818654</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6283,7 +6293,9 @@
       <c r="G112" t="n">
         <v>3594.3313</v>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="n">
+        <v>3600</v>
+      </c>
       <c r="I112" t="n">
         <v>5.669</v>
       </c>
@@ -6293,7 +6305,7 @@
         </is>
       </c>
       <c r="K112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6472,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:05:56.239790+00:00</t>
+          <t>2026-10-03T00:06:47.787035+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:06:47.787035+00:00</t>
+          <t>2026-10-03T00:07:39.702237+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:07:39.702237+00:00</t>
+          <t>2026-10-03T00:08:31.231177+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:08:31.231177+00:00</t>
+          <t>2026-10-03T00:09:22.355444+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:09:22.355444+00:00</t>
+          <t>2026-10-03T00:10:13.980163+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:10:13.980163+00:00</t>
+          <t>2026-10-03T00:11:05.127709+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:11:05.127709+00:00</t>
+          <t>2026-10-03T00:11:56.826766+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:11:56.826766+00:00</t>
+          <t>2026-10-03T00:12:48.034908+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:12:48.034908+00:00</t>
+          <t>2026-10-03T00:13:39.252664+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:13:39.252664+00:00</t>
+          <t>2026-10-03T00:14:31.195891+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:14:31.195891+00:00</t>
+          <t>2026-10-03T00:15:22.145251+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1047.2708</v>
+        <v>1047.46293867</v>
       </c>
       <c r="H2" t="n">
         <v>801351</v>
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,17 +1566,17 @@
         </is>
       </c>
       <c r="G7" t="n">
+        <v>2400.2944</v>
+      </c>
+      <c r="H7" t="n">
         <v>2400.4866</v>
       </c>
-      <c r="H7" t="n">
-        <v>3447.7573</v>
-      </c>
       <c r="I7" t="n">
-        <v>1047.271</v>
+        <v>0.192</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1594,16 +1594,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Senkova Aneta</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>821897</v>
+        <v>801351</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1611,17 +1611,17 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2427.8242</v>
+        <v>2400.4866</v>
       </c>
       <c r="H8" t="n">
-        <v>2480.845</v>
+        <v>3447.7573</v>
       </c>
       <c r="I8" t="n">
-        <v>53.021</v>
+        <v>1047.271</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>17.27</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1639,16 +1639,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>816244</v>
+        <v>821897</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,17 +1656,17 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2438.9453</v>
+        <v>2427.8242</v>
       </c>
       <c r="H9" t="n">
-        <v>2512.1113</v>
+        <v>2480.845</v>
       </c>
       <c r="I9" t="n">
-        <v>73.166</v>
+        <v>53.021</v>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>818654</v>
+        <v>816244</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1701,17 +1701,17 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2441.7278</v>
+        <v>2438.9453</v>
       </c>
       <c r="H10" t="n">
-        <v>2491.449</v>
+        <v>2512.1113</v>
       </c>
       <c r="I10" t="n">
-        <v>49.721</v>
+        <v>73.166</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,17 +1746,17 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2478.4348</v>
+        <v>2441.7278</v>
       </c>
       <c r="H11" t="n">
-        <v>2520.9268</v>
+        <v>2491.449</v>
       </c>
       <c r="I11" t="n">
-        <v>42.492</v>
+        <v>49.721</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1774,16 +1774,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>906527</v>
+        <v>801538</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,17 +1791,17 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2480.845</v>
+        <v>2478.4348</v>
       </c>
       <c r="H12" t="n">
         <v>2520.9268</v>
       </c>
       <c r="I12" t="n">
-        <v>40.082</v>
+        <v>42.492</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1819,16 +1819,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>822077</v>
+        <v>906527</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1839,14 +1839,14 @@
         <v>2480.845</v>
       </c>
       <c r="H13" t="n">
-        <v>2600.113</v>
+        <v>2520.9268</v>
       </c>
       <c r="I13" t="n">
-        <v>119.268</v>
+        <v>40.082</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>816647</v>
+        <v>822077</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1881,17 +1881,17 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2491.449</v>
+        <v>2480.845</v>
       </c>
       <c r="H14" t="n">
-        <v>2592.934</v>
+        <v>2600.113</v>
       </c>
       <c r="I14" t="n">
-        <v>101.485</v>
+        <v>119.268</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1909,16 +1909,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,17 +1926,17 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2512.1113</v>
+        <v>2491.449</v>
       </c>
       <c r="H15" t="n">
         <v>2592.934</v>
       </c>
       <c r="I15" t="n">
-        <v>80.82299999999999</v>
+        <v>101.485</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1954,16 +1954,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kaitlyn Mallette</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>847128</v>
+        <v>847129</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1971,17 +1971,17 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2520.9268</v>
+        <v>2512.1113</v>
       </c>
       <c r="H16" t="n">
-        <v>2593.3486</v>
+        <v>2592.934</v>
       </c>
       <c r="I16" t="n">
-        <v>72.422</v>
+        <v>80.82299999999999</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1999,16 +1999,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Kaitlyn Mallette</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>816596</v>
+        <v>847128</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         <v>2520.9268</v>
       </c>
       <c r="H17" t="n">
-        <v>2592.934</v>
+        <v>2593.3486</v>
       </c>
       <c r="I17" t="n">
-        <v>72.00700000000001</v>
+        <v>72.422</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -2044,16 +2044,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gabrielle Lalonde</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>856725</v>
+        <v>816596</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2061,17 +2061,17 @@
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2520.9268</v>
+      </c>
+      <c r="H18" t="n">
         <v>2592.934</v>
       </c>
-      <c r="H18" t="n">
-        <v>2600.113</v>
-      </c>
       <c r="I18" t="n">
-        <v>7.179</v>
+        <v>72.00700000000001</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2089,16 +2089,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Abby Richardson</t>
+          <t>Gabrielle Lalonde</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>824230</v>
+        <v>856725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Abby Richardson</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>822075</v>
+        <v>824230</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>835282</v>
+        <v>822075</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2196,17 +2196,17 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2593.3486</v>
+        <v>2592.934</v>
       </c>
       <c r="H21" t="n">
-        <v>2655.681</v>
+        <v>2600.113</v>
       </c>
       <c r="I21" t="n">
-        <v>62.332</v>
+        <v>7.179</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2224,16 +2224,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,17 +2241,17 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2600.113</v>
+        <v>2593.3486</v>
       </c>
       <c r="H22" t="n">
         <v>2655.681</v>
       </c>
       <c r="I22" t="n">
-        <v>55.568</v>
+        <v>62.332</v>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2269,16 +2269,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>891409</v>
+        <v>816275</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2289,14 +2289,14 @@
         <v>2600.113</v>
       </c>
       <c r="H23" t="n">
-        <v>2651.5955</v>
+        <v>2655.681</v>
       </c>
       <c r="I23" t="n">
-        <v>51.482</v>
+        <v>55.568</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2314,16 +2314,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2334,14 +2334,14 @@
         <v>2600.113</v>
       </c>
       <c r="H24" t="n">
-        <v>2648.6033</v>
+        <v>2651.5955</v>
       </c>
       <c r="I24" t="n">
-        <v>48.49</v>
+        <v>51.482</v>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2359,16 +2359,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>801530</v>
+        <v>811470</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2379,14 +2379,14 @@
         <v>2600.113</v>
       </c>
       <c r="H25" t="n">
-        <v>2659.2349</v>
+        <v>2648.6033</v>
       </c>
       <c r="I25" t="n">
-        <v>59.122</v>
+        <v>48.49</v>
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>818654</v>
+        <v>801530</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2648.6033</v>
+        <v>2600.113</v>
       </c>
       <c r="H26" t="n">
-        <v>2698.6963</v>
+        <v>2659.2349</v>
       </c>
       <c r="I26" t="n">
-        <v>50.093</v>
+        <v>59.122</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>816244</v>
+        <v>818654</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2466,17 +2466,17 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2651.5955</v>
+        <v>2648.6033</v>
       </c>
       <c r="H27" t="n">
         <v>2698.6963</v>
       </c>
       <c r="I27" t="n">
-        <v>47.101</v>
+        <v>50.093</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>822077</v>
+        <v>816244</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2655.681</v>
+        <v>2651.5955</v>
       </c>
       <c r="H28" t="n">
-        <v>2667.7725</v>
+        <v>2698.6963</v>
       </c>
       <c r="I28" t="n">
-        <v>12.092</v>
+        <v>47.101</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -2539,16 +2539,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>856721</v>
+        <v>822077</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2584,16 +2584,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>801538</v>
+        <v>856721</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2601,17 +2601,17 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2659.2349</v>
+        <v>2655.681</v>
       </c>
       <c r="H30" t="n">
-        <v>2698.6963</v>
+        <v>2667.7725</v>
       </c>
       <c r="I30" t="n">
-        <v>39.461</v>
+        <v>12.092</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -2629,16 +2629,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>906527</v>
+        <v>801538</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2646,17 +2646,17 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2667.7725</v>
+        <v>2659.2349</v>
       </c>
       <c r="H31" t="n">
-        <v>2711.627</v>
+        <v>2698.6963</v>
       </c>
       <c r="I31" t="n">
-        <v>43.854</v>
+        <v>39.461</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -2674,16 +2674,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>821897</v>
+        <v>906527</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2719,16 +2719,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>816596</v>
+        <v>821897</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2736,17 +2736,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2698.6963</v>
+        <v>2667.7725</v>
       </c>
       <c r="H33" t="n">
-        <v>2725.247</v>
+        <v>2711.627</v>
       </c>
       <c r="I33" t="n">
-        <v>26.551</v>
+        <v>43.854</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -2764,16 +2764,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>847129</v>
+        <v>816596</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>822077</v>
+        <v>816647</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2871,17 +2871,17 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2711.627</v>
+        <v>2698.6963</v>
       </c>
       <c r="H36" t="n">
         <v>2725.247</v>
       </c>
       <c r="I36" t="n">
-        <v>13.62</v>
+        <v>26.551</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -2899,16 +2899,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>856721</v>
+        <v>822077</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2944,34 +2944,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>801538</v>
+        <v>856721</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>2711.627</v>
+      </c>
+      <c r="H38" t="n">
         <v>2725.247</v>
       </c>
-      <c r="H38" t="n">
-        <v>2772.9321</v>
-      </c>
       <c r="I38" t="n">
-        <v>47.685</v>
+        <v>13.62</v>
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -2989,16 +2989,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3009,14 +3009,14 @@
         <v>2725.247</v>
       </c>
       <c r="H39" t="n">
-        <v>2789.0894</v>
+        <v>2772.9321</v>
       </c>
       <c r="I39" t="n">
-        <v>63.842</v>
+        <v>47.685</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>816275</v>
+        <v>818654</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3079,16 +3079,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>821897</v>
+        <v>816275</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3124,16 +3124,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>816647</v>
+        <v>821897</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3141,17 +3141,17 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2772.9321</v>
+        <v>2725.247</v>
       </c>
       <c r="H42" t="n">
-        <v>2819.3076</v>
+        <v>2789.0894</v>
       </c>
       <c r="I42" t="n">
-        <v>46.375</v>
+        <v>63.842</v>
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>822075</v>
+        <v>816647</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3186,17 +3186,17 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2789.0894</v>
+        <v>2772.9321</v>
       </c>
       <c r="H43" t="n">
         <v>2819.3076</v>
       </c>
       <c r="I43" t="n">
-        <v>30.218</v>
+        <v>46.375</v>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>822077</v>
+        <v>822075</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3234,14 +3234,14 @@
         <v>2789.0894</v>
       </c>
       <c r="H44" t="n">
-        <v>2853.243</v>
+        <v>2819.3076</v>
       </c>
       <c r="I44" t="n">
-        <v>64.154</v>
+        <v>30.218</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -3259,16 +3259,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>835282</v>
+        <v>822077</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3304,16 +3304,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>801530</v>
+        <v>835282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3321,17 +3321,17 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2819.3076</v>
+        <v>2789.0894</v>
       </c>
       <c r="H46" t="n">
-        <v>2864.9006</v>
+        <v>2853.243</v>
       </c>
       <c r="I46" t="n">
-        <v>45.593</v>
+        <v>64.154</v>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K46" t="b">
@@ -3349,16 +3349,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3369,14 +3369,14 @@
         <v>2819.3076</v>
       </c>
       <c r="H47" t="n">
-        <v>2880.334</v>
+        <v>2864.9006</v>
       </c>
       <c r="I47" t="n">
-        <v>61.026</v>
+        <v>45.593</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -3394,34 +3394,34 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>816596</v>
+        <v>811470</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2846.4148</v>
+        <v>2819.3076</v>
       </c>
       <c r="H48" t="n">
-        <v>2904.394</v>
+        <v>2880.334</v>
       </c>
       <c r="I48" t="n">
-        <v>57.979</v>
+        <v>61.026</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -3439,16 +3439,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>821897</v>
+        <v>816596</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3456,17 +3456,17 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2853.243</v>
+        <v>2846.4148</v>
       </c>
       <c r="H49" t="n">
         <v>2904.394</v>
       </c>
       <c r="I49" t="n">
-        <v>51.151</v>
+        <v>57.979</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -3484,16 +3484,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>816275</v>
+        <v>821897</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3529,16 +3529,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>816647</v>
+        <v>816275</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3546,17 +3546,17 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>2864.9006</v>
+        <v>2853.243</v>
       </c>
       <c r="H51" t="n">
         <v>2904.394</v>
       </c>
       <c r="I51" t="n">
-        <v>39.493</v>
+        <v>51.151</v>
       </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K51" t="b">
@@ -3574,16 +3574,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2880.334</v>
+        <v>2864.9006</v>
       </c>
       <c r="H52" t="n">
         <v>2904.394</v>
       </c>
       <c r="I52" t="n">
-        <v>24.06</v>
+        <v>39.493</v>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -3619,16 +3619,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>822077</v>
+        <v>847129</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3636,17 +3636,17 @@
         </is>
       </c>
       <c r="G53" t="n">
+        <v>2880.334</v>
+      </c>
+      <c r="H53" t="n">
         <v>2904.394</v>
       </c>
-      <c r="H53" t="n">
-        <v>2960.5295</v>
-      </c>
       <c r="I53" t="n">
-        <v>56.135</v>
+        <v>24.06</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K53" t="b">
@@ -3664,16 +3664,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>818654</v>
+        <v>822077</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3684,14 +3684,14 @@
         <v>2904.394</v>
       </c>
       <c r="H54" t="n">
-        <v>2955.026</v>
+        <v>2960.5295</v>
       </c>
       <c r="I54" t="n">
-        <v>50.632</v>
+        <v>56.135</v>
       </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K54" t="b">
@@ -3709,16 +3709,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3754,16 +3754,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>816244</v>
+        <v>801538</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3799,16 +3799,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>906527</v>
+        <v>816244</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3819,14 +3819,14 @@
         <v>2904.394</v>
       </c>
       <c r="H57" t="n">
-        <v>2960.5295</v>
+        <v>2955.026</v>
       </c>
       <c r="I57" t="n">
-        <v>56.135</v>
+        <v>50.632</v>
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K57" t="b">
@@ -3844,16 +3844,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>891409</v>
+        <v>906527</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2955.026</v>
+        <v>2904.394</v>
       </c>
       <c r="H58" t="n">
-        <v>3011.4944</v>
+        <v>2960.5295</v>
       </c>
       <c r="I58" t="n">
-        <v>56.469</v>
+        <v>56.135</v>
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
@@ -3889,16 +3889,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3934,16 +3934,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>801530</v>
+        <v>811470</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3979,16 +3979,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>835282</v>
+        <v>801530</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3996,13 +3996,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2960.5295</v>
+        <v>2955.026</v>
       </c>
       <c r="H61" t="n">
-        <v>3016.6372</v>
+        <v>3011.4944</v>
       </c>
       <c r="I61" t="n">
-        <v>56.108</v>
+        <v>56.469</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
@@ -4024,16 +4024,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4069,16 +4069,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>816596</v>
+        <v>816275</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4086,17 +4086,17 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3011.4944</v>
+        <v>2960.5295</v>
       </c>
       <c r="H63" t="n">
-        <v>3041.6526</v>
+        <v>3016.6372</v>
       </c>
       <c r="I63" t="n">
-        <v>30.158</v>
+        <v>56.108</v>
       </c>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K63" t="b">
@@ -4114,16 +4114,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>816647</v>
+        <v>816596</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4134,14 +4134,14 @@
         <v>3011.4944</v>
       </c>
       <c r="H64" t="n">
-        <v>3056.29</v>
+        <v>3041.6526</v>
       </c>
       <c r="I64" t="n">
-        <v>44.796</v>
+        <v>30.158</v>
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K64" t="b">
@@ -4159,16 +4159,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4204,16 +4204,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>821897</v>
+        <v>847129</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>3016.6372</v>
+        <v>3011.4944</v>
       </c>
       <c r="H66" t="n">
-        <v>3096.3313</v>
+        <v>3056.29</v>
       </c>
       <c r="I66" t="n">
-        <v>79.694</v>
+        <v>44.796</v>
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K66" t="b">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>906527</v>
+        <v>821897</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>822075</v>
+        <v>906527</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4311,17 +4311,17 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3041.6526</v>
+        <v>3016.6372</v>
       </c>
       <c r="H68" t="n">
         <v>3096.3313</v>
       </c>
       <c r="I68" t="n">
-        <v>54.679</v>
+        <v>79.694</v>
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K68" t="b">
@@ -4339,16 +4339,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Abby Richardson</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>824230</v>
+        <v>822075</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4356,17 +4356,17 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>3056.29</v>
+        <v>3041.6526</v>
       </c>
       <c r="H69" t="n">
         <v>3096.3313</v>
       </c>
       <c r="I69" t="n">
-        <v>40.041</v>
+        <v>54.679</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K69" t="b">
@@ -4384,16 +4384,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Gabrielle Lalonde</t>
+          <t>Abby Richardson</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>856725</v>
+        <v>824230</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4404,14 +4404,14 @@
         <v>3056.29</v>
       </c>
       <c r="H70" t="n">
-        <v>3093.9167</v>
+        <v>3096.3313</v>
       </c>
       <c r="I70" t="n">
-        <v>37.627</v>
+        <v>40.041</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K70" t="b">
@@ -4429,16 +4429,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Gabrielle Lalonde</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>818654</v>
+        <v>856725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4446,17 +4446,17 @@
         </is>
       </c>
       <c r="G71" t="n">
+        <v>3056.29</v>
+      </c>
+      <c r="H71" t="n">
         <v>3093.9167</v>
       </c>
-      <c r="H71" t="n">
-        <v>3144.6514</v>
-      </c>
       <c r="I71" t="n">
-        <v>50.735</v>
+        <v>37.627</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K71" t="b">
@@ -4474,16 +4474,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4491,17 +4491,17 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3096.3313</v>
+        <v>3093.9167</v>
       </c>
       <c r="H72" t="n">
         <v>3144.6514</v>
       </c>
       <c r="I72" t="n">
-        <v>48.32</v>
+        <v>50.735</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K72" t="b">
@@ -4519,16 +4519,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>816244</v>
+        <v>801538</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>816275</v>
+        <v>816244</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4609,16 +4609,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>835282</v>
+        <v>816275</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4654,16 +4654,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>801530</v>
+        <v>835282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4671,17 +4671,17 @@
         </is>
       </c>
       <c r="G76" t="n">
+        <v>3096.3313</v>
+      </c>
+      <c r="H76" t="n">
         <v>3144.6514</v>
       </c>
-      <c r="H76" t="n">
-        <v>3168.7314</v>
-      </c>
       <c r="I76" t="n">
-        <v>24.08</v>
+        <v>48.32</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K76" t="b">
@@ -4699,16 +4699,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>891409</v>
+        <v>801530</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4744,16 +4744,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4789,16 +4789,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>821897</v>
+        <v>811470</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4809,14 +4809,14 @@
         <v>3144.6514</v>
       </c>
       <c r="H79" t="n">
-        <v>3182.4758</v>
+        <v>3168.7314</v>
       </c>
       <c r="I79" t="n">
-        <v>37.824</v>
+        <v>24.08</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K79" t="b">
@@ -4834,16 +4834,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>906527</v>
+        <v>821897</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4854,14 +4854,14 @@
         <v>3144.6514</v>
       </c>
       <c r="H80" t="n">
-        <v>3195.1514</v>
+        <v>3182.4758</v>
       </c>
       <c r="I80" t="n">
-        <v>50.5</v>
+        <v>37.824</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K80" t="b">
@@ -4879,16 +4879,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>816596</v>
+        <v>906527</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4896,17 +4896,17 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>3168.7314</v>
+        <v>3144.6514</v>
       </c>
       <c r="H81" t="n">
-        <v>3214.8923</v>
+        <v>3195.1514</v>
       </c>
       <c r="I81" t="n">
-        <v>46.161</v>
+        <v>50.5</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K81" t="b">
@@ -4924,16 +4924,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>816647</v>
+        <v>816596</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4969,16 +4969,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5014,16 +5014,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>822077</v>
+        <v>847129</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5031,17 +5031,17 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>3182.4758</v>
+        <v>3168.7314</v>
       </c>
       <c r="H84" t="n">
         <v>3214.8923</v>
       </c>
       <c r="I84" t="n">
-        <v>32.417</v>
+        <v>46.161</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K84" t="b">
@@ -5059,16 +5059,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>856721</v>
+        <v>822077</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5076,17 +5076,17 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>3195.1514</v>
+        <v>3182.4758</v>
       </c>
       <c r="H85" t="n">
         <v>3214.8923</v>
       </c>
       <c r="I85" t="n">
-        <v>19.741</v>
+        <v>32.417</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K85" t="b">
@@ -5104,16 +5104,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>816275</v>
+        <v>856721</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5121,17 +5121,17 @@
         </is>
       </c>
       <c r="G86" t="n">
+        <v>3195.1514</v>
+      </c>
+      <c r="H86" t="n">
         <v>3214.8923</v>
       </c>
-      <c r="H86" t="n">
-        <v>3282.735</v>
-      </c>
       <c r="I86" t="n">
-        <v>67.843</v>
+        <v>19.741</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="K86" t="b">
@@ -5149,16 +5149,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>835282</v>
+        <v>816275</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5169,14 +5169,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H87" t="n">
-        <v>3296.4724</v>
+        <v>3282.735</v>
       </c>
       <c r="I87" t="n">
-        <v>81.58</v>
+        <v>67.843</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K87" t="b">
@@ -5194,16 +5194,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>801538</v>
+        <v>835282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5214,14 +5214,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H88" t="n">
-        <v>3255.0747</v>
+        <v>3296.4724</v>
       </c>
       <c r="I88" t="n">
-        <v>40.182</v>
+        <v>81.58</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K88" t="b">
@@ -5239,16 +5239,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>816244</v>
+        <v>801538</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5284,16 +5284,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>818654</v>
+        <v>816244</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5304,14 +5304,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H90" t="n">
-        <v>3278.2192</v>
+        <v>3255.0747</v>
       </c>
       <c r="I90" t="n">
-        <v>63.327</v>
+        <v>40.182</v>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K90" t="b">
@@ -5329,16 +5329,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>801530</v>
+        <v>818654</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5346,17 +5346,17 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3255.0747</v>
+        <v>3214.8923</v>
       </c>
       <c r="H91" t="n">
-        <v>3309.288</v>
+        <v>3278.2192</v>
       </c>
       <c r="I91" t="n">
-        <v>54.213</v>
+        <v>63.327</v>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="K91" t="b">
@@ -5374,16 +5374,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5394,14 +5394,14 @@
         <v>3255.0747</v>
       </c>
       <c r="H92" t="n">
-        <v>3312.039</v>
+        <v>3309.288</v>
       </c>
       <c r="I92" t="n">
-        <v>56.964</v>
+        <v>54.213</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="K92" t="b">
@@ -5419,16 +5419,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>891409</v>
+        <v>811470</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5436,17 +5436,17 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>3278.2192</v>
+        <v>3255.0747</v>
       </c>
       <c r="H93" t="n">
         <v>3312.039</v>
       </c>
       <c r="I93" t="n">
-        <v>33.82</v>
+        <v>56.964</v>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K93" t="b">
@@ -5464,16 +5464,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>821897</v>
+        <v>891409</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5481,17 +5481,17 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>3282.735</v>
+        <v>3278.2192</v>
       </c>
       <c r="H94" t="n">
-        <v>3385.5386</v>
+        <v>3312.039</v>
       </c>
       <c r="I94" t="n">
-        <v>102.803</v>
+        <v>33.82</v>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K94" t="b">
@@ -5509,16 +5509,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>906527</v>
+        <v>821897</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5526,17 +5526,17 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3296.4724</v>
+        <v>3282.735</v>
       </c>
       <c r="H95" t="n">
         <v>3385.5386</v>
       </c>
       <c r="I95" t="n">
-        <v>89.066</v>
+        <v>102.803</v>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K95" t="b">
@@ -5554,16 +5554,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>816596</v>
+        <v>906527</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5571,17 +5571,17 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3309.609</v>
+        <v>3296.4724</v>
       </c>
       <c r="H96" t="n">
-        <v>3361.359</v>
+        <v>3385.5386</v>
       </c>
       <c r="I96" t="n">
-        <v>51.75</v>
+        <v>89.066</v>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K96" t="b">
@@ -5599,16 +5599,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>816647</v>
+        <v>816596</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5616,17 +5616,17 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>3312.039</v>
+        <v>3309.609</v>
       </c>
       <c r="H97" t="n">
-        <v>3380.4558</v>
+        <v>3361.359</v>
       </c>
       <c r="I97" t="n">
-        <v>68.417</v>
+        <v>51.75</v>
       </c>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K97" t="b">
@@ -5644,16 +5644,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5689,16 +5689,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>801538</v>
+        <v>847129</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5706,17 +5706,17 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3361.359</v>
+        <v>3312.039</v>
       </c>
       <c r="H99" t="n">
-        <v>3393.143</v>
+        <v>3380.4558</v>
       </c>
       <c r="I99" t="n">
-        <v>31.784</v>
+        <v>68.417</v>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K99" t="b">
@@ -5734,16 +5734,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5751,17 +5751,17 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3380.4558</v>
+        <v>3361.359</v>
       </c>
       <c r="H100" t="n">
         <v>3393.143</v>
       </c>
       <c r="I100" t="n">
-        <v>12.687</v>
+        <v>31.784</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K100" t="b">
@@ -5779,16 +5779,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>816244</v>
+        <v>818654</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5824,16 +5824,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>816275</v>
+        <v>816244</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5841,17 +5841,17 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3385.5386</v>
+        <v>3380.4558</v>
       </c>
       <c r="H102" t="n">
-        <v>3600</v>
+        <v>3393.143</v>
       </c>
       <c r="I102" t="n">
-        <v>214.461</v>
+        <v>12.687</v>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K102" t="b">
@@ -5869,16 +5869,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>835282</v>
+        <v>816275</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5914,16 +5914,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>811470</v>
+        <v>835282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5931,17 +5931,17 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3393.143</v>
+        <v>3385.5386</v>
       </c>
       <c r="H104" t="n">
-        <v>3548.692</v>
+        <v>3600</v>
       </c>
       <c r="I104" t="n">
-        <v>155.549</v>
+        <v>214.461</v>
       </c>
       <c r="J104" s="1" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K104" t="b">
@@ -5959,16 +5959,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>891409</v>
+        <v>811470</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5979,14 +5979,14 @@
         <v>3393.143</v>
       </c>
       <c r="H105" t="n">
-        <v>3447.7573</v>
+        <v>3548.692</v>
       </c>
       <c r="I105" t="n">
-        <v>54.614</v>
+        <v>155.549</v>
       </c>
       <c r="J105" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K105" t="b">
@@ -6004,16 +6004,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>801530</v>
+        <v>891409</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6024,14 +6024,14 @@
         <v>3393.143</v>
       </c>
       <c r="H106" t="n">
-        <v>3600</v>
+        <v>3447.7573</v>
       </c>
       <c r="I106" t="n">
-        <v>206.857</v>
+        <v>54.614</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K106" t="b">
@@ -6049,16 +6049,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>801538</v>
+        <v>801530</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6066,17 +6066,17 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>3447.7573</v>
+        <v>3393.143</v>
       </c>
       <c r="H107" t="n">
         <v>3600</v>
       </c>
       <c r="I107" t="n">
-        <v>152.243</v>
+        <v>206.857</v>
       </c>
       <c r="J107" s="1" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="K107" t="b">
@@ -6094,16 +6094,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6114,14 +6114,14 @@
         <v>3447.7573</v>
       </c>
       <c r="H108" t="n">
-        <v>3550.9062</v>
+        <v>3600</v>
       </c>
       <c r="I108" t="n">
-        <v>103.149</v>
+        <v>152.243</v>
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K108" t="b">
@@ -6139,16 +6139,16 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>891409</v>
+        <v>818654</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6156,17 +6156,17 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3548.692</v>
+        <v>3447.7573</v>
       </c>
       <c r="H109" t="n">
-        <v>3594.3313</v>
+        <v>3550.9062</v>
       </c>
       <c r="I109" t="n">
-        <v>45.639</v>
+        <v>103.149</v>
       </c>
       <c r="J109" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K109" t="b">
@@ -6184,16 +6184,16 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>816244</v>
+        <v>891409</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6201,17 +6201,17 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3550.9062</v>
+        <v>3548.692</v>
       </c>
       <c r="H110" t="n">
         <v>3594.3313</v>
       </c>
       <c r="I110" t="n">
-        <v>43.425</v>
+        <v>45.639</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K110" t="b">
@@ -6229,16 +6229,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>811470</v>
+        <v>816244</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6246,17 +6246,17 @@
         </is>
       </c>
       <c r="G111" t="n">
+        <v>3550.9062</v>
+      </c>
+      <c r="H111" t="n">
         <v>3594.3313</v>
       </c>
-      <c r="H111" t="n">
-        <v>3600</v>
-      </c>
       <c r="I111" t="n">
-        <v>5.669</v>
+        <v>43.425</v>
       </c>
       <c r="J111" s="1" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="K111" t="b">
@@ -6274,16 +6274,16 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>818654</v>
+        <v>811470</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6305,6 +6305,51 @@
         </is>
       </c>
       <c r="K112" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>3</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Janelle Evans</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>818654</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>3594.3313</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.669</v>
+      </c>
+      <c r="J113" s="1" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K113" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6484,7 +6529,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:15:22.145251+00:00</t>
+          <t>2026-10-03T00:16:14.371755+00:00</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:16:14.371755+00:00</t>
+          <t>2026-10-03T00:17:05.657891+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:17:05.657891+00:00</t>
+          <t>2026-10-03T00:17:57.384892+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -477,12 +477,16 @@
           <t>Senkova Aneta</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -490,7 +494,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1047.46293867</v>
+        <v>1047.26317867</v>
       </c>
       <c r="H2" t="n">
         <v>801351</v>
@@ -521,15 +525,15 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>10.08</t>
+          <t>10.07</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>607.505625</v>
+        <v>607.4057715</v>
       </c>
       <c r="H3" t="n">
         <v>835282</v>
@@ -599,7 +603,7 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
@@ -607,7 +611,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>524.474118</v>
+        <v>524.374264</v>
       </c>
       <c r="H5" t="n">
         <v>801530</v>
@@ -716,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
@@ -724,7 +728,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>449.680421</v>
+        <v>449.580568</v>
       </c>
       <c r="H8" t="n">
         <v>811470</v>
@@ -950,7 +954,7 @@
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
@@ -958,7 +962,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>297.685306</v>
+        <v>297.5854525</v>
       </c>
       <c r="H14" t="n">
         <v>822077</v>
@@ -1253,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,14 +1618,14 @@
         <v>2400.4866</v>
       </c>
       <c r="H8" t="n">
-        <v>3447.7573</v>
+        <v>2725.1472</v>
       </c>
       <c r="I8" t="n">
-        <v>1047.271</v>
+        <v>324.661</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -2989,16 +2993,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Senkova Aneta</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>801538</v>
+        <v>801351</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3009,14 +3013,14 @@
         <v>2725.247</v>
       </c>
       <c r="H39" t="n">
-        <v>2772.9321</v>
+        <v>2845.2412</v>
       </c>
       <c r="I39" t="n">
-        <v>47.685</v>
+        <v>119.994</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -3034,16 +3038,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3054,14 +3058,14 @@
         <v>2725.247</v>
       </c>
       <c r="H40" t="n">
-        <v>2789.0894</v>
+        <v>2772.9321</v>
       </c>
       <c r="I40" t="n">
-        <v>63.842</v>
+        <v>47.685</v>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -3079,16 +3083,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>816275</v>
+        <v>818654</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3124,16 +3128,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>821897</v>
+        <v>816275</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3169,16 +3173,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>816647</v>
+        <v>821897</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3186,17 +3190,17 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2772.9321</v>
+        <v>2725.247</v>
       </c>
       <c r="H43" t="n">
-        <v>2819.3076</v>
+        <v>2789.0894</v>
       </c>
       <c r="I43" t="n">
-        <v>46.375</v>
+        <v>63.842</v>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -3214,16 +3218,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>822075</v>
+        <v>816647</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3231,17 +3235,17 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2789.0894</v>
+        <v>2772.9321</v>
       </c>
       <c r="H44" t="n">
         <v>2819.3076</v>
       </c>
       <c r="I44" t="n">
-        <v>30.218</v>
+        <v>46.375</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -3259,16 +3263,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>822077</v>
+        <v>822075</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3279,14 +3283,14 @@
         <v>2789.0894</v>
       </c>
       <c r="H45" t="n">
-        <v>2853.243</v>
+        <v>2819.3076</v>
       </c>
       <c r="I45" t="n">
-        <v>64.154</v>
+        <v>30.218</v>
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K45" t="b">
@@ -3304,16 +3308,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>835282</v>
+        <v>822077</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3324,14 +3328,14 @@
         <v>2789.0894</v>
       </c>
       <c r="H46" t="n">
-        <v>2853.243</v>
+        <v>2845.2412</v>
       </c>
       <c r="I46" t="n">
-        <v>64.154</v>
+        <v>56.152</v>
       </c>
       <c r="J46" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K46" t="b">
@@ -3349,16 +3353,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>801530</v>
+        <v>835282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3366,17 +3370,17 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2819.3076</v>
+        <v>2789.0894</v>
       </c>
       <c r="H47" t="n">
-        <v>2864.9006</v>
+        <v>2845.2412</v>
       </c>
       <c r="I47" t="n">
-        <v>45.593</v>
+        <v>56.152</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -3394,16 +3398,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3414,14 +3418,14 @@
         <v>2819.3076</v>
       </c>
       <c r="H48" t="n">
-        <v>2880.334</v>
+        <v>2845.2412</v>
       </c>
       <c r="I48" t="n">
-        <v>61.026</v>
+        <v>25.934</v>
       </c>
       <c r="J48" s="1" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -3439,34 +3443,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>816596</v>
+        <v>811470</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2846.4148</v>
+        <v>2819.3076</v>
       </c>
       <c r="H49" t="n">
-        <v>2904.394</v>
+        <v>2845.2412</v>
       </c>
       <c r="I49" t="n">
-        <v>57.979</v>
+        <v>25.934</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -3484,16 +3488,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>821897</v>
+        <v>822077</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3501,17 +3505,17 @@
         </is>
       </c>
       <c r="G50" t="n">
+        <v>2845.341</v>
+      </c>
+      <c r="H50" t="n">
         <v>2853.243</v>
       </c>
-      <c r="H50" t="n">
-        <v>2904.394</v>
-      </c>
       <c r="I50" t="n">
-        <v>51.151</v>
+        <v>7.902</v>
       </c>
       <c r="J50" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="K50" t="b">
@@ -3529,16 +3533,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3546,17 +3550,17 @@
         </is>
       </c>
       <c r="G51" t="n">
+        <v>2845.341</v>
+      </c>
+      <c r="H51" t="n">
         <v>2853.243</v>
       </c>
-      <c r="H51" t="n">
-        <v>2904.394</v>
-      </c>
       <c r="I51" t="n">
-        <v>51.151</v>
+        <v>7.902</v>
       </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="K51" t="b">
@@ -3574,16 +3578,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>816647</v>
+        <v>811470</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3591,17 +3595,17 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>2864.9006</v>
+        <v>2845.341</v>
       </c>
       <c r="H52" t="n">
-        <v>2904.394</v>
+        <v>2880.334</v>
       </c>
       <c r="I52" t="n">
-        <v>39.493</v>
+        <v>34.993</v>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -3619,16 +3623,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>847129</v>
+        <v>801530</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3636,17 +3640,17 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2880.334</v>
+        <v>2845.341</v>
       </c>
       <c r="H53" t="n">
-        <v>2904.394</v>
+        <v>2864.9006</v>
       </c>
       <c r="I53" t="n">
-        <v>24.06</v>
+        <v>19.56</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="K53" t="b">
@@ -3664,16 +3668,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Senkova Aneta</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>822077</v>
+        <v>801351</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3681,17 +3685,17 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2904.394</v>
+        <v>2845.341</v>
       </c>
       <c r="H54" t="n">
-        <v>2960.5295</v>
+        <v>3447.7573</v>
       </c>
       <c r="I54" t="n">
-        <v>56.135</v>
+        <v>602.4160000000001</v>
       </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="K54" t="b">
@@ -3709,16 +3713,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>818654</v>
+        <v>816596</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3726,17 +3730,17 @@
         </is>
       </c>
       <c r="G55" t="n">
+        <v>2846.4148</v>
+      </c>
+      <c r="H55" t="n">
         <v>2904.394</v>
       </c>
-      <c r="H55" t="n">
-        <v>2955.026</v>
-      </c>
       <c r="I55" t="n">
-        <v>50.632</v>
+        <v>57.979</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K55" t="b">
@@ -3754,16 +3758,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>801538</v>
+        <v>821897</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3771,13 +3775,13 @@
         </is>
       </c>
       <c r="G56" t="n">
+        <v>2853.243</v>
+      </c>
+      <c r="H56" t="n">
         <v>2904.394</v>
       </c>
-      <c r="H56" t="n">
-        <v>2955.026</v>
-      </c>
       <c r="I56" t="n">
-        <v>50.632</v>
+        <v>51.151</v>
       </c>
       <c r="J56" s="1" t="inlineStr">
         <is>
@@ -3799,16 +3803,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>816244</v>
+        <v>816275</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3816,13 +3820,13 @@
         </is>
       </c>
       <c r="G57" t="n">
+        <v>2853.243</v>
+      </c>
+      <c r="H57" t="n">
         <v>2904.394</v>
       </c>
-      <c r="H57" t="n">
-        <v>2955.026</v>
-      </c>
       <c r="I57" t="n">
-        <v>50.632</v>
+        <v>51.151</v>
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
@@ -3844,16 +3848,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>906527</v>
+        <v>816647</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3861,17 +3865,17 @@
         </is>
       </c>
       <c r="G58" t="n">
+        <v>2864.9006</v>
+      </c>
+      <c r="H58" t="n">
         <v>2904.394</v>
       </c>
-      <c r="H58" t="n">
-        <v>2960.5295</v>
-      </c>
       <c r="I58" t="n">
-        <v>56.135</v>
+        <v>39.493</v>
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -3889,16 +3893,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>891409</v>
+        <v>847129</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3906,17 +3910,17 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2955.026</v>
+        <v>2880.334</v>
       </c>
       <c r="H59" t="n">
-        <v>3011.4944</v>
+        <v>2904.394</v>
       </c>
       <c r="I59" t="n">
-        <v>56.469</v>
+        <v>24.06</v>
       </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K59" t="b">
@@ -3934,16 +3938,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>811470</v>
+        <v>822077</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3951,13 +3955,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>2955.026</v>
+        <v>2904.394</v>
       </c>
       <c r="H60" t="n">
-        <v>3011.4944</v>
+        <v>2960.5295</v>
       </c>
       <c r="I60" t="n">
-        <v>56.469</v>
+        <v>56.135</v>
       </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
@@ -3979,16 +3983,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>801530</v>
+        <v>818654</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3996,17 +4000,17 @@
         </is>
       </c>
       <c r="G61" t="n">
+        <v>2904.394</v>
+      </c>
+      <c r="H61" t="n">
         <v>2955.026</v>
       </c>
-      <c r="H61" t="n">
-        <v>3011.4944</v>
-      </c>
       <c r="I61" t="n">
-        <v>56.469</v>
+        <v>50.632</v>
       </c>
       <c r="J61" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K61" t="b">
@@ -4024,16 +4028,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>835282</v>
+        <v>801538</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4041,17 +4045,17 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2960.5295</v>
+        <v>2904.394</v>
       </c>
       <c r="H62" t="n">
-        <v>3016.6372</v>
+        <v>2955.026</v>
       </c>
       <c r="I62" t="n">
-        <v>56.108</v>
+        <v>50.632</v>
       </c>
       <c r="J62" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K62" t="b">
@@ -4069,16 +4073,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>816275</v>
+        <v>816244</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4086,17 +4090,17 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>2960.5295</v>
+        <v>2904.394</v>
       </c>
       <c r="H63" t="n">
-        <v>3016.6372</v>
+        <v>2955.026</v>
       </c>
       <c r="I63" t="n">
-        <v>56.108</v>
+        <v>50.632</v>
       </c>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K63" t="b">
@@ -4114,16 +4118,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>816596</v>
+        <v>906527</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4131,17 +4135,17 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>3011.4944</v>
+        <v>2904.394</v>
       </c>
       <c r="H64" t="n">
-        <v>3041.6526</v>
+        <v>2960.5295</v>
       </c>
       <c r="I64" t="n">
-        <v>30.158</v>
+        <v>56.135</v>
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K64" t="b">
@@ -4159,16 +4163,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>816647</v>
+        <v>891409</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4176,17 +4180,17 @@
         </is>
       </c>
       <c r="G65" t="n">
+        <v>2955.026</v>
+      </c>
+      <c r="H65" t="n">
         <v>3011.4944</v>
       </c>
-      <c r="H65" t="n">
-        <v>3056.29</v>
-      </c>
       <c r="I65" t="n">
-        <v>44.796</v>
+        <v>56.469</v>
       </c>
       <c r="J65" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K65" t="b">
@@ -4204,16 +4208,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>847129</v>
+        <v>811470</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4221,17 +4225,17 @@
         </is>
       </c>
       <c r="G66" t="n">
+        <v>2955.026</v>
+      </c>
+      <c r="H66" t="n">
         <v>3011.4944</v>
       </c>
-      <c r="H66" t="n">
-        <v>3056.29</v>
-      </c>
       <c r="I66" t="n">
-        <v>44.796</v>
+        <v>56.469</v>
       </c>
       <c r="J66" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K66" t="b">
@@ -4249,16 +4253,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>821897</v>
+        <v>801530</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4266,17 +4270,17 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>3016.6372</v>
+        <v>2955.026</v>
       </c>
       <c r="H67" t="n">
-        <v>3096.3313</v>
+        <v>3011.4944</v>
       </c>
       <c r="I67" t="n">
-        <v>79.694</v>
+        <v>56.469</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K67" t="b">
@@ -4294,16 +4298,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>906527</v>
+        <v>835282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4311,17 +4315,17 @@
         </is>
       </c>
       <c r="G68" t="n">
+        <v>2960.5295</v>
+      </c>
+      <c r="H68" t="n">
         <v>3016.6372</v>
       </c>
-      <c r="H68" t="n">
-        <v>3096.3313</v>
-      </c>
       <c r="I68" t="n">
-        <v>79.694</v>
+        <v>56.108</v>
       </c>
       <c r="J68" s="1" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K68" t="b">
@@ -4339,16 +4343,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>822075</v>
+        <v>816275</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4356,17 +4360,17 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>3041.6526</v>
+        <v>2960.5295</v>
       </c>
       <c r="H69" t="n">
-        <v>3096.3313</v>
+        <v>3016.6372</v>
       </c>
       <c r="I69" t="n">
-        <v>54.679</v>
+        <v>56.108</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K69" t="b">
@@ -4384,16 +4388,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Abby Richardson</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>824230</v>
+        <v>816596</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4401,17 +4405,17 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>3056.29</v>
+        <v>3011.4944</v>
       </c>
       <c r="H70" t="n">
-        <v>3096.3313</v>
+        <v>3041.6526</v>
       </c>
       <c r="I70" t="n">
-        <v>40.041</v>
+        <v>30.158</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K70" t="b">
@@ -4429,16 +4433,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Gabrielle Lalonde</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>856725</v>
+        <v>816647</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4446,17 +4450,17 @@
         </is>
       </c>
       <c r="G71" t="n">
+        <v>3011.4944</v>
+      </c>
+      <c r="H71" t="n">
         <v>3056.29</v>
       </c>
-      <c r="H71" t="n">
-        <v>3093.9167</v>
-      </c>
       <c r="I71" t="n">
-        <v>37.627</v>
+        <v>44.796</v>
       </c>
       <c r="J71" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K71" t="b">
@@ -4474,16 +4478,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>818654</v>
+        <v>847129</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4491,17 +4495,17 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3093.9167</v>
+        <v>3011.4944</v>
       </c>
       <c r="H72" t="n">
-        <v>3144.6514</v>
+        <v>3056.29</v>
       </c>
       <c r="I72" t="n">
-        <v>50.735</v>
+        <v>44.796</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K72" t="b">
@@ -4519,16 +4523,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>801538</v>
+        <v>821897</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4536,17 +4540,17 @@
         </is>
       </c>
       <c r="G73" t="n">
+        <v>3016.6372</v>
+      </c>
+      <c r="H73" t="n">
         <v>3096.3313</v>
       </c>
-      <c r="H73" t="n">
-        <v>3144.6514</v>
-      </c>
       <c r="I73" t="n">
-        <v>48.32</v>
+        <v>79.694</v>
       </c>
       <c r="J73" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K73" t="b">
@@ -4564,16 +4568,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>816244</v>
+        <v>906527</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4581,17 +4585,17 @@
         </is>
       </c>
       <c r="G74" t="n">
+        <v>3016.6372</v>
+      </c>
+      <c r="H74" t="n">
         <v>3096.3313</v>
       </c>
-      <c r="H74" t="n">
-        <v>3144.6514</v>
-      </c>
       <c r="I74" t="n">
-        <v>48.32</v>
+        <v>79.694</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K74" t="b">
@@ -4609,16 +4613,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>816275</v>
+        <v>822075</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4626,17 +4630,17 @@
         </is>
       </c>
       <c r="G75" t="n">
+        <v>3041.6526</v>
+      </c>
+      <c r="H75" t="n">
         <v>3096.3313</v>
       </c>
-      <c r="H75" t="n">
-        <v>3144.6514</v>
-      </c>
       <c r="I75" t="n">
-        <v>48.32</v>
+        <v>54.679</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K75" t="b">
@@ -4654,16 +4658,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Abby Richardson</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>835282</v>
+        <v>824230</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4671,17 +4675,17 @@
         </is>
       </c>
       <c r="G76" t="n">
+        <v>3056.29</v>
+      </c>
+      <c r="H76" t="n">
         <v>3096.3313</v>
       </c>
-      <c r="H76" t="n">
-        <v>3144.6514</v>
-      </c>
       <c r="I76" t="n">
-        <v>48.32</v>
+        <v>40.041</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K76" t="b">
@@ -4699,16 +4703,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Gabrielle Lalonde</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>801530</v>
+        <v>856725</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4716,17 +4720,17 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>3144.6514</v>
+        <v>3056.29</v>
       </c>
       <c r="H77" t="n">
-        <v>3168.7314</v>
+        <v>3093.9167</v>
       </c>
       <c r="I77" t="n">
-        <v>24.08</v>
+        <v>37.627</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K77" t="b">
@@ -4744,16 +4748,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>891409</v>
+        <v>818654</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4761,17 +4765,17 @@
         </is>
       </c>
       <c r="G78" t="n">
+        <v>3093.9167</v>
+      </c>
+      <c r="H78" t="n">
         <v>3144.6514</v>
       </c>
-      <c r="H78" t="n">
-        <v>3168.7314</v>
-      </c>
       <c r="I78" t="n">
-        <v>24.08</v>
+        <v>50.735</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K78" t="b">
@@ -4789,16 +4793,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>811470</v>
+        <v>801538</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4806,17 +4810,17 @@
         </is>
       </c>
       <c r="G79" t="n">
+        <v>3096.3313</v>
+      </c>
+      <c r="H79" t="n">
         <v>3144.6514</v>
       </c>
-      <c r="H79" t="n">
-        <v>3168.7314</v>
-      </c>
       <c r="I79" t="n">
-        <v>24.08</v>
+        <v>48.32</v>
       </c>
       <c r="J79" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K79" t="b">
@@ -4834,16 +4838,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>821897</v>
+        <v>816244</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4851,17 +4855,17 @@
         </is>
       </c>
       <c r="G80" t="n">
+        <v>3096.3313</v>
+      </c>
+      <c r="H80" t="n">
         <v>3144.6514</v>
       </c>
-      <c r="H80" t="n">
-        <v>3182.4758</v>
-      </c>
       <c r="I80" t="n">
-        <v>37.824</v>
+        <v>48.32</v>
       </c>
       <c r="J80" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K80" t="b">
@@ -4879,16 +4883,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>906527</v>
+        <v>816275</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4896,17 +4900,17 @@
         </is>
       </c>
       <c r="G81" t="n">
+        <v>3096.3313</v>
+      </c>
+      <c r="H81" t="n">
         <v>3144.6514</v>
       </c>
-      <c r="H81" t="n">
-        <v>3195.1514</v>
-      </c>
       <c r="I81" t="n">
-        <v>50.5</v>
+        <v>48.32</v>
       </c>
       <c r="J81" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K81" t="b">
@@ -4924,16 +4928,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>816596</v>
+        <v>835282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4941,17 +4945,17 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3168.7314</v>
+        <v>3096.3313</v>
       </c>
       <c r="H82" t="n">
-        <v>3214.8923</v>
+        <v>3144.6514</v>
       </c>
       <c r="I82" t="n">
-        <v>46.161</v>
+        <v>48.32</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K82" t="b">
@@ -4969,16 +4973,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>816647</v>
+        <v>801530</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4986,17 +4990,17 @@
         </is>
       </c>
       <c r="G83" t="n">
+        <v>3144.6514</v>
+      </c>
+      <c r="H83" t="n">
         <v>3168.7314</v>
       </c>
-      <c r="H83" t="n">
-        <v>3214.8923</v>
-      </c>
       <c r="I83" t="n">
-        <v>46.161</v>
+        <v>24.08</v>
       </c>
       <c r="J83" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K83" t="b">
@@ -5014,16 +5018,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>847129</v>
+        <v>891409</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5031,17 +5035,17 @@
         </is>
       </c>
       <c r="G84" t="n">
+        <v>3144.6514</v>
+      </c>
+      <c r="H84" t="n">
         <v>3168.7314</v>
       </c>
-      <c r="H84" t="n">
-        <v>3214.8923</v>
-      </c>
       <c r="I84" t="n">
-        <v>46.161</v>
+        <v>24.08</v>
       </c>
       <c r="J84" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K84" t="b">
@@ -5059,16 +5063,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>822077</v>
+        <v>811470</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5076,17 +5080,17 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>3182.4758</v>
+        <v>3144.6514</v>
       </c>
       <c r="H85" t="n">
-        <v>3214.8923</v>
+        <v>3168.7314</v>
       </c>
       <c r="I85" t="n">
-        <v>32.417</v>
+        <v>24.08</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K85" t="b">
@@ -5104,16 +5108,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>856721</v>
+        <v>821897</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5121,17 +5125,17 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>3195.1514</v>
+        <v>3144.6514</v>
       </c>
       <c r="H86" t="n">
-        <v>3214.8923</v>
+        <v>3182.4758</v>
       </c>
       <c r="I86" t="n">
-        <v>19.741</v>
+        <v>37.824</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K86" t="b">
@@ -5149,16 +5153,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>816275</v>
+        <v>906527</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5166,17 +5170,17 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3214.8923</v>
+        <v>3144.6514</v>
       </c>
       <c r="H87" t="n">
-        <v>3282.735</v>
+        <v>3195.1514</v>
       </c>
       <c r="I87" t="n">
-        <v>67.843</v>
+        <v>50.5</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K87" t="b">
@@ -5194,16 +5198,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>835282</v>
+        <v>816596</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5211,17 +5215,17 @@
         </is>
       </c>
       <c r="G88" t="n">
+        <v>3168.7314</v>
+      </c>
+      <c r="H88" t="n">
         <v>3214.8923</v>
       </c>
-      <c r="H88" t="n">
-        <v>3296.4724</v>
-      </c>
       <c r="I88" t="n">
-        <v>81.58</v>
+        <v>46.161</v>
       </c>
       <c r="J88" s="1" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K88" t="b">
@@ -5239,16 +5243,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>801538</v>
+        <v>816647</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5256,17 +5260,17 @@
         </is>
       </c>
       <c r="G89" t="n">
+        <v>3168.7314</v>
+      </c>
+      <c r="H89" t="n">
         <v>3214.8923</v>
       </c>
-      <c r="H89" t="n">
-        <v>3255.0747</v>
-      </c>
       <c r="I89" t="n">
-        <v>40.182</v>
+        <v>46.161</v>
       </c>
       <c r="J89" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K89" t="b">
@@ -5284,16 +5288,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>816244</v>
+        <v>847129</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5301,17 +5305,17 @@
         </is>
       </c>
       <c r="G90" t="n">
+        <v>3168.7314</v>
+      </c>
+      <c r="H90" t="n">
         <v>3214.8923</v>
       </c>
-      <c r="H90" t="n">
-        <v>3255.0747</v>
-      </c>
       <c r="I90" t="n">
-        <v>40.182</v>
+        <v>46.161</v>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K90" t="b">
@@ -5329,16 +5333,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>818654</v>
+        <v>822077</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5346,17 +5350,17 @@
         </is>
       </c>
       <c r="G91" t="n">
+        <v>3182.4758</v>
+      </c>
+      <c r="H91" t="n">
         <v>3214.8923</v>
       </c>
-      <c r="H91" t="n">
-        <v>3278.2192</v>
-      </c>
       <c r="I91" t="n">
-        <v>63.327</v>
+        <v>32.417</v>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K91" t="b">
@@ -5374,16 +5378,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>801530</v>
+        <v>856721</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5391,17 +5395,17 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>3255.0747</v>
+        <v>3195.1514</v>
       </c>
       <c r="H92" t="n">
-        <v>3309.288</v>
+        <v>3214.8923</v>
       </c>
       <c r="I92" t="n">
-        <v>54.213</v>
+        <v>19.741</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="K92" t="b">
@@ -5419,16 +5423,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>811470</v>
+        <v>816275</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5436,17 +5440,17 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>3255.0747</v>
+        <v>3214.8923</v>
       </c>
       <c r="H93" t="n">
-        <v>3312.039</v>
+        <v>3282.735</v>
       </c>
       <c r="I93" t="n">
-        <v>56.964</v>
+        <v>67.843</v>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K93" t="b">
@@ -5464,16 +5468,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>891409</v>
+        <v>835282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5481,17 +5485,17 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>3278.2192</v>
+        <v>3214.8923</v>
       </c>
       <c r="H94" t="n">
-        <v>3312.039</v>
+        <v>3296.4724</v>
       </c>
       <c r="I94" t="n">
-        <v>33.82</v>
+        <v>81.58</v>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K94" t="b">
@@ -5509,16 +5513,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>821897</v>
+        <v>801538</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5526,17 +5530,17 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3282.735</v>
+        <v>3214.8923</v>
       </c>
       <c r="H95" t="n">
-        <v>3385.5386</v>
+        <v>3255.0747</v>
       </c>
       <c r="I95" t="n">
-        <v>102.803</v>
+        <v>40.182</v>
       </c>
       <c r="J95" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K95" t="b">
@@ -5554,16 +5558,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>906527</v>
+        <v>816244</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5571,17 +5575,17 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>3296.4724</v>
+        <v>3214.8923</v>
       </c>
       <c r="H96" t="n">
-        <v>3385.5386</v>
+        <v>3255.0747</v>
       </c>
       <c r="I96" t="n">
-        <v>89.066</v>
+        <v>40.182</v>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K96" t="b">
@@ -5599,16 +5603,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>816596</v>
+        <v>818654</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5616,17 +5620,17 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>3309.609</v>
+        <v>3214.8923</v>
       </c>
       <c r="H97" t="n">
-        <v>3361.359</v>
+        <v>3278.2192</v>
       </c>
       <c r="I97" t="n">
-        <v>51.75</v>
+        <v>63.327</v>
       </c>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="K97" t="b">
@@ -5644,16 +5648,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>816647</v>
+        <v>801530</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5661,17 +5665,17 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>3312.039</v>
+        <v>3255.0747</v>
       </c>
       <c r="H98" t="n">
-        <v>3380.4558</v>
+        <v>3309.288</v>
       </c>
       <c r="I98" t="n">
-        <v>68.417</v>
+        <v>54.213</v>
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="K98" t="b">
@@ -5689,16 +5693,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>847129</v>
+        <v>811470</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5706,17 +5710,17 @@
         </is>
       </c>
       <c r="G99" t="n">
+        <v>3255.0747</v>
+      </c>
+      <c r="H99" t="n">
         <v>3312.039</v>
       </c>
-      <c r="H99" t="n">
-        <v>3380.4558</v>
-      </c>
       <c r="I99" t="n">
-        <v>68.417</v>
+        <v>56.964</v>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K99" t="b">
@@ -5734,16 +5738,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>801538</v>
+        <v>891409</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5751,17 +5755,17 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3361.359</v>
+        <v>3278.2192</v>
       </c>
       <c r="H100" t="n">
-        <v>3393.143</v>
+        <v>3312.039</v>
       </c>
       <c r="I100" t="n">
-        <v>31.784</v>
+        <v>33.82</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K100" t="b">
@@ -5779,16 +5783,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>818654</v>
+        <v>821897</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5796,17 +5800,17 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3380.4558</v>
+        <v>3282.735</v>
       </c>
       <c r="H101" t="n">
-        <v>3393.143</v>
+        <v>3385.5386</v>
       </c>
       <c r="I101" t="n">
-        <v>12.687</v>
+        <v>102.803</v>
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K101" t="b">
@@ -5824,16 +5828,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>816244</v>
+        <v>906527</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5841,17 +5845,17 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3380.4558</v>
+        <v>3296.4724</v>
       </c>
       <c r="H102" t="n">
-        <v>3393.143</v>
+        <v>3385.5386</v>
       </c>
       <c r="I102" t="n">
-        <v>12.687</v>
+        <v>89.066</v>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K102" t="b">
@@ -5869,16 +5873,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>816275</v>
+        <v>816596</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5886,17 +5890,17 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3385.5386</v>
+        <v>3309.609</v>
       </c>
       <c r="H103" t="n">
-        <v>3600</v>
+        <v>3361.359</v>
       </c>
       <c r="I103" t="n">
-        <v>214.461</v>
+        <v>51.75</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K103" t="b">
@@ -5914,16 +5918,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>835282</v>
+        <v>816647</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5931,17 +5935,17 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>3385.5386</v>
+        <v>3312.039</v>
       </c>
       <c r="H104" t="n">
-        <v>3600</v>
+        <v>3380.4558</v>
       </c>
       <c r="I104" t="n">
-        <v>214.461</v>
+        <v>68.417</v>
       </c>
       <c r="J104" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K104" t="b">
@@ -5959,16 +5963,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>811470</v>
+        <v>847129</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5976,17 +5980,17 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3393.143</v>
+        <v>3312.039</v>
       </c>
       <c r="H105" t="n">
-        <v>3548.692</v>
+        <v>3380.4558</v>
       </c>
       <c r="I105" t="n">
-        <v>155.549</v>
+        <v>68.417</v>
       </c>
       <c r="J105" s="1" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K105" t="b">
@@ -6004,16 +6008,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>891409</v>
+        <v>801538</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6021,17 +6025,17 @@
         </is>
       </c>
       <c r="G106" t="n">
+        <v>3361.359</v>
+      </c>
+      <c r="H106" t="n">
         <v>3393.143</v>
       </c>
-      <c r="H106" t="n">
-        <v>3447.7573</v>
-      </c>
       <c r="I106" t="n">
-        <v>54.614</v>
+        <v>31.784</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K106" t="b">
@@ -6049,16 +6053,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>801530</v>
+        <v>818654</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6066,17 +6070,17 @@
         </is>
       </c>
       <c r="G107" t="n">
+        <v>3380.4558</v>
+      </c>
+      <c r="H107" t="n">
         <v>3393.143</v>
       </c>
-      <c r="H107" t="n">
-        <v>3600</v>
-      </c>
       <c r="I107" t="n">
-        <v>206.857</v>
+        <v>12.687</v>
       </c>
       <c r="J107" s="1" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K107" t="b">
@@ -6094,16 +6098,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>801538</v>
+        <v>816244</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6111,17 +6115,17 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3447.7573</v>
+        <v>3380.4558</v>
       </c>
       <c r="H108" t="n">
-        <v>3600</v>
+        <v>3393.143</v>
       </c>
       <c r="I108" t="n">
-        <v>152.243</v>
+        <v>12.687</v>
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K108" t="b">
@@ -6139,16 +6143,16 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>818654</v>
+        <v>816275</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6156,17 +6160,17 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3447.7573</v>
+        <v>3385.5386</v>
       </c>
       <c r="H109" t="n">
-        <v>3550.9062</v>
+        <v>3600</v>
       </c>
       <c r="I109" t="n">
-        <v>103.149</v>
+        <v>214.461</v>
       </c>
       <c r="J109" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K109" t="b">
@@ -6184,16 +6188,16 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>891409</v>
+        <v>835282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6201,17 +6205,17 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3548.692</v>
+        <v>3385.5386</v>
       </c>
       <c r="H110" t="n">
-        <v>3594.3313</v>
+        <v>3600</v>
       </c>
       <c r="I110" t="n">
-        <v>45.639</v>
+        <v>214.461</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K110" t="b">
@@ -6229,16 +6233,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>816244</v>
+        <v>811470</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6246,17 +6250,17 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3550.9062</v>
+        <v>3393.143</v>
       </c>
       <c r="H111" t="n">
-        <v>3594.3313</v>
+        <v>3548.692</v>
       </c>
       <c r="I111" t="n">
-        <v>43.425</v>
+        <v>155.549</v>
       </c>
       <c r="J111" s="1" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K111" t="b">
@@ -6274,16 +6278,16 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6291,17 +6295,17 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>3594.3313</v>
+        <v>3393.143</v>
       </c>
       <c r="H112" t="n">
-        <v>3600</v>
+        <v>3447.7573</v>
       </c>
       <c r="I112" t="n">
-        <v>5.669</v>
+        <v>54.614</v>
       </c>
       <c r="J112" s="1" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K112" t="b">
@@ -6319,16 +6323,16 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>818654</v>
+        <v>801530</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6336,20 +6340,290 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>3594.3313</v>
+        <v>3393.143</v>
       </c>
       <c r="H113" t="n">
         <v>3600</v>
       </c>
       <c r="I113" t="n">
+        <v>206.857</v>
+      </c>
+      <c r="J113" s="1" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
+      <c r="K113" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>3</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Jessie Pellerin</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>801538</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>3447.7573</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I114" t="n">
+        <v>152.243</v>
+      </c>
+      <c r="J114" s="1" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="K114" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Janelle Evans</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>818654</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>3447.7573</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3550.9062</v>
+      </c>
+      <c r="I115" t="n">
+        <v>103.149</v>
+      </c>
+      <c r="J115" s="1" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="K115" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Kennedy Sisson</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>891409</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>3548.692</v>
+      </c>
+      <c r="H116" t="n">
+        <v>3594.3313</v>
+      </c>
+      <c r="I116" t="n">
+        <v>45.639</v>
+      </c>
+      <c r="J116" s="1" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="K116" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>3</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Isa Goettl</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>816244</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>3550.9062</v>
+      </c>
+      <c r="H117" t="n">
+        <v>3594.3313</v>
+      </c>
+      <c r="I117" t="n">
+        <v>43.425</v>
+      </c>
+      <c r="J117" s="1" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="K117" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Manon le Scodan</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>811470</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>3594.3313</v>
+      </c>
+      <c r="H118" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I118" t="n">
         <v>5.669</v>
       </c>
-      <c r="J113" s="1" t="inlineStr">
+      <c r="J118" s="1" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="K113" t="b">
+      <c r="K118" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CUGN</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Janelle Evans</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>818654</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>3594.3313</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3600</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5.669</v>
+      </c>
+      <c r="J119" s="1" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="K119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6529,7 +6803,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:17:57.384892+00:00</t>
+          <t>2026-10-03T00:18:48.643484+00:00</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6814,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16">

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:18:48.643484+00:00</t>
+          <t>2026-10-03T00:19:41.163120+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:19:41.163120+00:00</t>
+          <t>2026-10-03T00:20:32.598247+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6803,7 +6803,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:20:32.598247+00:00</t>
+          <t>2026-10-03T00:21:24.212673+00:00</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="B16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -477,11 +477,7 @@
           <t>Senkova Aneta</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>3</v>
       </c>
@@ -6803,7 +6799,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:21:24.212673+00:00</t>
+          <t>2026-10-03T00:22:15.568106+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -482,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1047.26317867</v>
+        <v>1047.26318</v>
       </c>
       <c r="H2" t="n">
         <v>801351</v>
@@ -1253,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,14 +1569,14 @@
         <v>2400.2944</v>
       </c>
       <c r="H7" t="n">
-        <v>2400.4866</v>
+        <v>2725.1472</v>
       </c>
       <c r="I7" t="n">
-        <v>0.192</v>
+        <v>324.853</v>
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -1594,16 +1594,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Senkova Aneta</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>801351</v>
+        <v>821897</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1611,17 +1611,17 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2400.4866</v>
+        <v>2427.8242</v>
       </c>
       <c r="H8" t="n">
-        <v>2725.1472</v>
+        <v>2480.845</v>
       </c>
       <c r="I8" t="n">
-        <v>324.661</v>
+        <v>53.021</v>
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -1639,16 +1639,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>821897</v>
+        <v>816244</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1656,17 +1656,17 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2427.8242</v>
+        <v>2438.9453</v>
       </c>
       <c r="H9" t="n">
-        <v>2480.845</v>
+        <v>2512.1113</v>
       </c>
       <c r="I9" t="n">
-        <v>53.021</v>
+        <v>73.166</v>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>816244</v>
+        <v>818654</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1701,17 +1701,17 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2438.9453</v>
+        <v>2441.7278</v>
       </c>
       <c r="H10" t="n">
-        <v>2512.1113</v>
+        <v>2491.449</v>
       </c>
       <c r="I10" t="n">
-        <v>73.166</v>
+        <v>49.721</v>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1746,17 +1746,17 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2441.7278</v>
+        <v>2478.4348</v>
       </c>
       <c r="H11" t="n">
-        <v>2491.449</v>
+        <v>2520.9268</v>
       </c>
       <c r="I11" t="n">
-        <v>49.721</v>
+        <v>42.492</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -1774,16 +1774,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>801538</v>
+        <v>906527</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1791,17 +1791,17 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2478.4348</v>
+        <v>2480.845</v>
       </c>
       <c r="H12" t="n">
         <v>2520.9268</v>
       </c>
       <c r="I12" t="n">
-        <v>42.492</v>
+        <v>40.082</v>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -1819,16 +1819,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>906527</v>
+        <v>822077</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1839,14 +1839,14 @@
         <v>2480.845</v>
       </c>
       <c r="H13" t="n">
-        <v>2520.9268</v>
+        <v>2600.113</v>
       </c>
       <c r="I13" t="n">
-        <v>40.082</v>
+        <v>119.268</v>
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>822077</v>
+        <v>816647</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1881,17 +1881,17 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2480.845</v>
+        <v>2491.449</v>
       </c>
       <c r="H14" t="n">
-        <v>2600.113</v>
+        <v>2592.934</v>
       </c>
       <c r="I14" t="n">
-        <v>119.268</v>
+        <v>101.485</v>
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -1909,16 +1909,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1926,17 +1926,17 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2491.449</v>
+        <v>2512.1113</v>
       </c>
       <c r="H15" t="n">
         <v>2592.934</v>
       </c>
       <c r="I15" t="n">
-        <v>101.485</v>
+        <v>80.82299999999999</v>
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -1954,16 +1954,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Kaitlyn Mallette</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>847129</v>
+        <v>847128</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1971,17 +1971,17 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2512.1113</v>
+        <v>2520.9268</v>
       </c>
       <c r="H16" t="n">
-        <v>2592.934</v>
+        <v>2593.3486</v>
       </c>
       <c r="I16" t="n">
-        <v>80.82299999999999</v>
+        <v>72.422</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -1999,16 +1999,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kaitlyn Mallette</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>847128</v>
+        <v>816596</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2019,10 +2019,10 @@
         <v>2520.9268</v>
       </c>
       <c r="H17" t="n">
-        <v>2593.3486</v>
+        <v>2592.934</v>
       </c>
       <c r="I17" t="n">
-        <v>72.422</v>
+        <v>72.00700000000001</v>
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
@@ -2044,16 +2044,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Gabrielle Lalonde</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>816596</v>
+        <v>856725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2061,17 +2061,17 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2520.9268</v>
+        <v>2592.934</v>
       </c>
       <c r="H18" t="n">
-        <v>2592.934</v>
+        <v>2600.113</v>
       </c>
       <c r="I18" t="n">
-        <v>72.00700000000001</v>
+        <v>7.179</v>
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -2089,16 +2089,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Gabrielle Lalonde</t>
+          <t>Abby Richardson</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>856725</v>
+        <v>824230</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2134,16 +2134,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Abby Richardson</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>824230</v>
+        <v>822075</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2179,16 +2179,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>822075</v>
+        <v>835282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2196,17 +2196,17 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2592.934</v>
+        <v>2593.3486</v>
       </c>
       <c r="H21" t="n">
-        <v>2600.113</v>
+        <v>2655.681</v>
       </c>
       <c r="I21" t="n">
-        <v>7.179</v>
+        <v>62.332</v>
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -2224,16 +2224,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>835282</v>
+        <v>816275</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2241,17 +2241,17 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2593.3486</v>
+        <v>2600.113</v>
       </c>
       <c r="H22" t="n">
         <v>2655.681</v>
       </c>
       <c r="I22" t="n">
-        <v>62.332</v>
+        <v>55.568</v>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -2269,16 +2269,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>816275</v>
+        <v>891409</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2289,14 +2289,14 @@
         <v>2600.113</v>
       </c>
       <c r="H23" t="n">
-        <v>2655.681</v>
+        <v>2651.5955</v>
       </c>
       <c r="I23" t="n">
-        <v>55.568</v>
+        <v>51.482</v>
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -2314,16 +2314,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>891409</v>
+        <v>811470</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2334,14 +2334,14 @@
         <v>2600.113</v>
       </c>
       <c r="H24" t="n">
-        <v>2651.5955</v>
+        <v>2648.6033</v>
       </c>
       <c r="I24" t="n">
-        <v>51.482</v>
+        <v>48.49</v>
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -2359,16 +2359,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2379,14 +2379,14 @@
         <v>2600.113</v>
       </c>
       <c r="H25" t="n">
-        <v>2648.6033</v>
+        <v>2659.2349</v>
       </c>
       <c r="I25" t="n">
-        <v>48.49</v>
+        <v>59.122</v>
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>801530</v>
+        <v>818654</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2600.113</v>
+        <v>2648.6033</v>
       </c>
       <c r="H26" t="n">
-        <v>2659.2349</v>
+        <v>2698.6963</v>
       </c>
       <c r="I26" t="n">
-        <v>59.122</v>
+        <v>50.093</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>818654</v>
+        <v>816244</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2466,17 +2466,17 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2648.6033</v>
+        <v>2651.5955</v>
       </c>
       <c r="H27" t="n">
         <v>2698.6963</v>
       </c>
       <c r="I27" t="n">
-        <v>50.093</v>
+        <v>47.101</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>816244</v>
+        <v>822077</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2651.5955</v>
+        <v>2655.681</v>
       </c>
       <c r="H28" t="n">
-        <v>2698.6963</v>
+        <v>2667.7725</v>
       </c>
       <c r="I28" t="n">
-        <v>47.101</v>
+        <v>12.092</v>
       </c>
       <c r="J28" s="1" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -2539,16 +2539,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>822077</v>
+        <v>856721</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2584,16 +2584,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>856721</v>
+        <v>801538</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2601,17 +2601,17 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2655.681</v>
+        <v>2659.2349</v>
       </c>
       <c r="H30" t="n">
-        <v>2667.7725</v>
+        <v>2698.6963</v>
       </c>
       <c r="I30" t="n">
-        <v>12.092</v>
+        <v>39.461</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -2629,16 +2629,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>801538</v>
+        <v>906527</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2646,17 +2646,17 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2659.2349</v>
+        <v>2667.7725</v>
       </c>
       <c r="H31" t="n">
-        <v>2698.6963</v>
+        <v>2711.627</v>
       </c>
       <c r="I31" t="n">
-        <v>39.461</v>
+        <v>43.854</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -2674,16 +2674,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>906527</v>
+        <v>821897</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2719,16 +2719,16 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>821897</v>
+        <v>816596</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2736,17 +2736,17 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2667.7725</v>
+        <v>2698.6963</v>
       </c>
       <c r="H33" t="n">
-        <v>2711.627</v>
+        <v>2725.247</v>
       </c>
       <c r="I33" t="n">
-        <v>43.854</v>
+        <v>26.551</v>
       </c>
       <c r="J33" s="1" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -2764,16 +2764,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>816596</v>
+        <v>847129</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2809,16 +2809,16 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>847129</v>
+        <v>816647</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2854,16 +2854,16 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>816647</v>
+        <v>822077</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2871,17 +2871,17 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2698.6963</v>
+        <v>2711.627</v>
       </c>
       <c r="H36" t="n">
         <v>2725.247</v>
       </c>
       <c r="I36" t="n">
-        <v>26.551</v>
+        <v>13.62</v>
       </c>
       <c r="J36" s="1" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -2899,16 +2899,16 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>822077</v>
+        <v>856721</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2944,34 +2944,34 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Senkova Aneta</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>856721</v>
+        <v>801351</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2711.627</v>
+        <v>2725.247</v>
       </c>
       <c r="H38" t="n">
-        <v>2725.247</v>
+        <v>2845.2412</v>
       </c>
       <c r="I38" t="n">
-        <v>13.62</v>
+        <v>119.994</v>
       </c>
       <c r="J38" s="1" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -2989,16 +2989,16 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Senkova Aneta</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>801351</v>
+        <v>801538</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3009,14 +3009,14 @@
         <v>2725.247</v>
       </c>
       <c r="H39" t="n">
-        <v>2845.2412</v>
+        <v>2772.9321</v>
       </c>
       <c r="I39" t="n">
-        <v>119.994</v>
+        <v>47.685</v>
       </c>
       <c r="J39" s="1" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3054,14 +3054,14 @@
         <v>2725.247</v>
       </c>
       <c r="H40" t="n">
-        <v>2772.9321</v>
+        <v>2789.0894</v>
       </c>
       <c r="I40" t="n">
-        <v>47.685</v>
+        <v>63.842</v>
       </c>
       <c r="J40" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -3079,16 +3079,16 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>818654</v>
+        <v>816275</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3124,16 +3124,16 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>816275</v>
+        <v>821897</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3169,16 +3169,16 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>821897</v>
+        <v>816647</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3186,17 +3186,17 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>2725.247</v>
+        <v>2772.9321</v>
       </c>
       <c r="H43" t="n">
-        <v>2789.0894</v>
+        <v>2819.3076</v>
       </c>
       <c r="I43" t="n">
-        <v>63.842</v>
+        <v>46.375</v>
       </c>
       <c r="J43" s="1" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>816647</v>
+        <v>822075</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3231,17 +3231,17 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2772.9321</v>
+        <v>2789.0894</v>
       </c>
       <c r="H44" t="n">
         <v>2819.3076</v>
       </c>
       <c r="I44" t="n">
-        <v>46.375</v>
+        <v>30.218</v>
       </c>
       <c r="J44" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -3259,16 +3259,16 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>822075</v>
+        <v>822077</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3279,14 +3279,14 @@
         <v>2789.0894</v>
       </c>
       <c r="H45" t="n">
-        <v>2819.3076</v>
+        <v>2845.2412</v>
       </c>
       <c r="I45" t="n">
-        <v>30.218</v>
+        <v>56.152</v>
       </c>
       <c r="J45" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K45" t="b">
@@ -3304,16 +3304,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>822077</v>
+        <v>835282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3349,16 +3349,16 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>835282</v>
+        <v>801530</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2789.0894</v>
+        <v>2819.3076</v>
       </c>
       <c r="H47" t="n">
         <v>2845.2412</v>
       </c>
       <c r="I47" t="n">
-        <v>56.152</v>
+        <v>25.934</v>
       </c>
       <c r="J47" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -3394,16 +3394,16 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>801530</v>
+        <v>811470</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3439,34 +3439,34 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>811470</v>
+        <v>822077</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2819.3076</v>
+        <v>2845.341</v>
       </c>
       <c r="H49" t="n">
-        <v>2845.2412</v>
+        <v>2853.243</v>
       </c>
       <c r="I49" t="n">
-        <v>25.934</v>
+        <v>7.902</v>
       </c>
       <c r="J49" s="1" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -3484,16 +3484,16 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>822077</v>
+        <v>835282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3529,16 +3529,16 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>835282</v>
+        <v>811470</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3549,14 +3549,14 @@
         <v>2845.341</v>
       </c>
       <c r="H51" t="n">
-        <v>2853.243</v>
+        <v>2880.334</v>
       </c>
       <c r="I51" t="n">
-        <v>7.902</v>
+        <v>34.993</v>
       </c>
       <c r="J51" s="1" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="K51" t="b">
@@ -3574,16 +3574,16 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3594,14 +3594,14 @@
         <v>2845.341</v>
       </c>
       <c r="H52" t="n">
-        <v>2880.334</v>
+        <v>2864.9006</v>
       </c>
       <c r="I52" t="n">
-        <v>34.993</v>
+        <v>19.56</v>
       </c>
       <c r="J52" s="1" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -3619,16 +3619,16 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Senkova Aneta</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>801530</v>
+        <v>801351</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3639,14 +3639,14 @@
         <v>2845.341</v>
       </c>
       <c r="H53" t="n">
-        <v>2864.9006</v>
+        <v>3447.7573</v>
       </c>
       <c r="I53" t="n">
-        <v>19.56</v>
+        <v>602.4160000000001</v>
       </c>
       <c r="J53" s="1" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>10.02</t>
         </is>
       </c>
       <c r="K53" t="b">
@@ -3664,16 +3664,16 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Senkova Aneta</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>801351</v>
+        <v>816596</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3681,17 +3681,17 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2845.341</v>
+        <v>2846.4148</v>
       </c>
       <c r="H54" t="n">
-        <v>3447.7573</v>
+        <v>2904.394</v>
       </c>
       <c r="I54" t="n">
-        <v>602.4160000000001</v>
+        <v>57.979</v>
       </c>
       <c r="J54" s="1" t="inlineStr">
         <is>
-          <t>10.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K54" t="b">
@@ -3709,16 +3709,16 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>816596</v>
+        <v>821897</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3726,17 +3726,17 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2846.4148</v>
+        <v>2853.243</v>
       </c>
       <c r="H55" t="n">
         <v>2904.394</v>
       </c>
       <c r="I55" t="n">
-        <v>57.979</v>
+        <v>51.151</v>
       </c>
       <c r="J55" s="1" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K55" t="b">
@@ -3754,16 +3754,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>821897</v>
+        <v>816275</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3799,16 +3799,16 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>816275</v>
+        <v>816647</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3816,17 +3816,17 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2853.243</v>
+        <v>2864.9006</v>
       </c>
       <c r="H57" t="n">
         <v>2904.394</v>
       </c>
       <c r="I57" t="n">
-        <v>51.151</v>
+        <v>39.493</v>
       </c>
       <c r="J57" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="K57" t="b">
@@ -3844,16 +3844,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3861,17 +3861,17 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2864.9006</v>
+        <v>2880.334</v>
       </c>
       <c r="H58" t="n">
         <v>2904.394</v>
       </c>
       <c r="I58" t="n">
-        <v>39.493</v>
+        <v>24.06</v>
       </c>
       <c r="J58" s="1" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -3889,16 +3889,16 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>847129</v>
+        <v>822077</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3906,17 +3906,17 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>2880.334</v>
+        <v>2904.394</v>
       </c>
       <c r="H59" t="n">
-        <v>2904.394</v>
+        <v>2960.5295</v>
       </c>
       <c r="I59" t="n">
-        <v>24.06</v>
+        <v>56.135</v>
       </c>
       <c r="J59" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K59" t="b">
@@ -3934,16 +3934,16 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>822077</v>
+        <v>818654</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3954,14 +3954,14 @@
         <v>2904.394</v>
       </c>
       <c r="H60" t="n">
-        <v>2960.5295</v>
+        <v>2955.026</v>
       </c>
       <c r="I60" t="n">
-        <v>56.135</v>
+        <v>50.632</v>
       </c>
       <c r="J60" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K60" t="b">
@@ -3979,16 +3979,16 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4024,16 +4024,16 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>801538</v>
+        <v>816244</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4069,16 +4069,16 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>816244</v>
+        <v>906527</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4089,14 +4089,14 @@
         <v>2904.394</v>
       </c>
       <c r="H63" t="n">
-        <v>2955.026</v>
+        <v>2960.5295</v>
       </c>
       <c r="I63" t="n">
-        <v>50.632</v>
+        <v>56.135</v>
       </c>
       <c r="J63" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K63" t="b">
@@ -4114,16 +4114,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>906527</v>
+        <v>891409</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>2904.394</v>
+        <v>2955.026</v>
       </c>
       <c r="H64" t="n">
-        <v>2960.5295</v>
+        <v>3011.4944</v>
       </c>
       <c r="I64" t="n">
-        <v>56.135</v>
+        <v>56.469</v>
       </c>
       <c r="J64" s="1" t="inlineStr">
         <is>
@@ -4159,16 +4159,16 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>891409</v>
+        <v>811470</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4204,16 +4204,16 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>811470</v>
+        <v>801530</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4249,16 +4249,16 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>801530</v>
+        <v>835282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4266,13 +4266,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2955.026</v>
+        <v>2960.5295</v>
       </c>
       <c r="H67" t="n">
-        <v>3011.4944</v>
+        <v>3016.6372</v>
       </c>
       <c r="I67" t="n">
-        <v>56.469</v>
+        <v>56.108</v>
       </c>
       <c r="J67" s="1" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>835282</v>
+        <v>816275</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4339,16 +4339,16 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>816275</v>
+        <v>816596</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4356,17 +4356,17 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2960.5295</v>
+        <v>3011.4944</v>
       </c>
       <c r="H69" t="n">
-        <v>3016.6372</v>
+        <v>3041.6526</v>
       </c>
       <c r="I69" t="n">
-        <v>56.108</v>
+        <v>30.158</v>
       </c>
       <c r="J69" s="1" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K69" t="b">
@@ -4384,16 +4384,16 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>816596</v>
+        <v>816647</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4404,14 +4404,14 @@
         <v>3011.4944</v>
       </c>
       <c r="H70" t="n">
-        <v>3041.6526</v>
+        <v>3056.29</v>
       </c>
       <c r="I70" t="n">
-        <v>30.158</v>
+        <v>44.796</v>
       </c>
       <c r="J70" s="1" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="K70" t="b">
@@ -4429,16 +4429,16 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>847129</v>
+        <v>821897</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4491,17 +4491,17 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>3011.4944</v>
+        <v>3016.6372</v>
       </c>
       <c r="H72" t="n">
-        <v>3056.29</v>
+        <v>3096.3313</v>
       </c>
       <c r="I72" t="n">
-        <v>44.796</v>
+        <v>79.694</v>
       </c>
       <c r="J72" s="1" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="K72" t="b">
@@ -4519,16 +4519,16 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>821897</v>
+        <v>906527</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Paige Wallace</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>906527</v>
+        <v>822075</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4581,17 +4581,17 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>3016.6372</v>
+        <v>3041.6526</v>
       </c>
       <c r="H74" t="n">
         <v>3096.3313</v>
       </c>
       <c r="I74" t="n">
-        <v>79.694</v>
+        <v>54.679</v>
       </c>
       <c r="J74" s="1" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K74" t="b">
@@ -4609,16 +4609,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Paige Wallace</t>
+          <t>Abby Richardson</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>822075</v>
+        <v>824230</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4626,17 +4626,17 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>3041.6526</v>
+        <v>3056.29</v>
       </c>
       <c r="H75" t="n">
         <v>3096.3313</v>
       </c>
       <c r="I75" t="n">
-        <v>54.679</v>
+        <v>40.041</v>
       </c>
       <c r="J75" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K75" t="b">
@@ -4654,16 +4654,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Abby Richardson</t>
+          <t>Gabrielle Lalonde</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>824230</v>
+        <v>856725</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4674,14 +4674,14 @@
         <v>3056.29</v>
       </c>
       <c r="H76" t="n">
-        <v>3096.3313</v>
+        <v>3093.9167</v>
       </c>
       <c r="I76" t="n">
-        <v>40.041</v>
+        <v>37.627</v>
       </c>
       <c r="J76" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K76" t="b">
@@ -4699,16 +4699,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Gabrielle Lalonde</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>856725</v>
+        <v>818654</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4716,17 +4716,17 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>3056.29</v>
+        <v>3093.9167</v>
       </c>
       <c r="H77" t="n">
-        <v>3093.9167</v>
+        <v>3144.6514</v>
       </c>
       <c r="I77" t="n">
-        <v>37.627</v>
+        <v>50.735</v>
       </c>
       <c r="J77" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="K77" t="b">
@@ -4744,16 +4744,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>818654</v>
+        <v>801538</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4761,17 +4761,17 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>3093.9167</v>
+        <v>3096.3313</v>
       </c>
       <c r="H78" t="n">
         <v>3144.6514</v>
       </c>
       <c r="I78" t="n">
-        <v>50.735</v>
+        <v>48.32</v>
       </c>
       <c r="J78" s="1" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="K78" t="b">
@@ -4789,16 +4789,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>801538</v>
+        <v>816244</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4834,16 +4834,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>816244</v>
+        <v>816275</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4879,16 +4879,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4924,16 +4924,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>835282</v>
+        <v>801530</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4941,17 +4941,17 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>3096.3313</v>
+        <v>3144.6514</v>
       </c>
       <c r="H82" t="n">
-        <v>3144.6514</v>
+        <v>3168.7314</v>
       </c>
       <c r="I82" t="n">
-        <v>48.32</v>
+        <v>24.08</v>
       </c>
       <c r="J82" s="1" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K82" t="b">
@@ -4969,16 +4969,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>801530</v>
+        <v>891409</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5014,16 +5014,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>891409</v>
+        <v>811470</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5059,16 +5059,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>811470</v>
+        <v>821897</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5079,14 +5079,14 @@
         <v>3144.6514</v>
       </c>
       <c r="H85" t="n">
-        <v>3168.7314</v>
+        <v>3182.4758</v>
       </c>
       <c r="I85" t="n">
-        <v>24.08</v>
+        <v>37.824</v>
       </c>
       <c r="J85" s="1" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K85" t="b">
@@ -5104,16 +5104,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>821897</v>
+        <v>906527</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5124,14 +5124,14 @@
         <v>3144.6514</v>
       </c>
       <c r="H86" t="n">
-        <v>3182.4758</v>
+        <v>3195.1514</v>
       </c>
       <c r="I86" t="n">
-        <v>37.824</v>
+        <v>50.5</v>
       </c>
       <c r="J86" s="1" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="K86" t="b">
@@ -5149,16 +5149,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>906527</v>
+        <v>816596</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5166,17 +5166,17 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>3144.6514</v>
+        <v>3168.7314</v>
       </c>
       <c r="H87" t="n">
-        <v>3195.1514</v>
+        <v>3214.8923</v>
       </c>
       <c r="I87" t="n">
-        <v>50.5</v>
+        <v>46.161</v>
       </c>
       <c r="J87" s="1" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K87" t="b">
@@ -5194,16 +5194,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>816596</v>
+        <v>816647</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5239,16 +5239,16 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5284,16 +5284,16 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Morgan Walton</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>847129</v>
+        <v>822077</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5301,17 +5301,17 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3168.7314</v>
+        <v>3182.4758</v>
       </c>
       <c r="H90" t="n">
         <v>3214.8923</v>
       </c>
       <c r="I90" t="n">
-        <v>46.161</v>
+        <v>32.417</v>
       </c>
       <c r="J90" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K90" t="b">
@@ -5329,16 +5329,16 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Morgan Walton</t>
+          <t>Jaela Carter</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>822077</v>
+        <v>856721</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5346,17 +5346,17 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3182.4758</v>
+        <v>3195.1514</v>
       </c>
       <c r="H91" t="n">
         <v>3214.8923</v>
       </c>
       <c r="I91" t="n">
-        <v>32.417</v>
+        <v>19.741</v>
       </c>
       <c r="J91" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="K91" t="b">
@@ -5374,16 +5374,16 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Jaela Carter</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>856721</v>
+        <v>816275</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5391,17 +5391,17 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>3195.1514</v>
+        <v>3214.8923</v>
       </c>
       <c r="H92" t="n">
-        <v>3214.8923</v>
+        <v>3282.735</v>
       </c>
       <c r="I92" t="n">
-        <v>19.741</v>
+        <v>67.843</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K92" t="b">
@@ -5419,16 +5419,16 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5439,14 +5439,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H93" t="n">
-        <v>3282.735</v>
+        <v>3296.4724</v>
       </c>
       <c r="I93" t="n">
-        <v>67.843</v>
+        <v>81.58</v>
       </c>
       <c r="J93" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="K93" t="b">
@@ -5464,16 +5464,16 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>835282</v>
+        <v>801538</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5484,14 +5484,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H94" t="n">
-        <v>3296.4724</v>
+        <v>3255.0747</v>
       </c>
       <c r="I94" t="n">
-        <v>81.58</v>
+        <v>40.182</v>
       </c>
       <c r="J94" s="1" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="K94" t="b">
@@ -5509,16 +5509,16 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>801538</v>
+        <v>816244</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5554,16 +5554,16 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>816244</v>
+        <v>818654</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5574,14 +5574,14 @@
         <v>3214.8923</v>
       </c>
       <c r="H96" t="n">
-        <v>3255.0747</v>
+        <v>3278.2192</v>
       </c>
       <c r="I96" t="n">
-        <v>40.182</v>
+        <v>63.327</v>
       </c>
       <c r="J96" s="1" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="K96" t="b">
@@ -5599,16 +5599,16 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>818654</v>
+        <v>801530</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5616,17 +5616,17 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>3214.8923</v>
+        <v>3255.0747</v>
       </c>
       <c r="H97" t="n">
-        <v>3278.2192</v>
+        <v>3309.288</v>
       </c>
       <c r="I97" t="n">
-        <v>63.327</v>
+        <v>54.213</v>
       </c>
       <c r="J97" s="1" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="K97" t="b">
@@ -5644,16 +5644,16 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>801530</v>
+        <v>811470</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5664,14 +5664,14 @@
         <v>3255.0747</v>
       </c>
       <c r="H98" t="n">
-        <v>3309.288</v>
+        <v>3312.039</v>
       </c>
       <c r="I98" t="n">
-        <v>54.213</v>
+        <v>56.964</v>
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="K98" t="b">
@@ -5689,16 +5689,16 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5706,17 +5706,17 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3255.0747</v>
+        <v>3278.2192</v>
       </c>
       <c r="H99" t="n">
         <v>3312.039</v>
       </c>
       <c r="I99" t="n">
-        <v>56.964</v>
+        <v>33.82</v>
       </c>
       <c r="J99" s="1" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="K99" t="b">
@@ -5734,16 +5734,16 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Sydney Lamb</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>891409</v>
+        <v>821897</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5751,17 +5751,17 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>3278.2192</v>
+        <v>3282.735</v>
       </c>
       <c r="H100" t="n">
-        <v>3312.039</v>
+        <v>3385.5386</v>
       </c>
       <c r="I100" t="n">
-        <v>33.82</v>
+        <v>102.803</v>
       </c>
       <c r="J100" s="1" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K100" t="b">
@@ -5779,16 +5779,16 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sydney Lamb</t>
+          <t>Ciara Lang</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>821897</v>
+        <v>906527</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5796,17 +5796,17 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>3282.735</v>
+        <v>3296.4724</v>
       </c>
       <c r="H101" t="n">
         <v>3385.5386</v>
       </c>
       <c r="I101" t="n">
-        <v>102.803</v>
+        <v>89.066</v>
       </c>
       <c r="J101" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="K101" t="b">
@@ -5824,16 +5824,16 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Ciara Lang</t>
+          <t>Shelby Laidlaw</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>906527</v>
+        <v>816596</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5841,17 +5841,17 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>3296.4724</v>
+        <v>3309.609</v>
       </c>
       <c r="H102" t="n">
-        <v>3385.5386</v>
+        <v>3361.359</v>
       </c>
       <c r="I102" t="n">
-        <v>89.066</v>
+        <v>51.75</v>
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="K102" t="b">
@@ -5869,16 +5869,16 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Shelby Laidlaw</t>
+          <t>Raedyn Spademan</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>816596</v>
+        <v>816647</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5886,17 +5886,17 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>3309.609</v>
+        <v>3312.039</v>
       </c>
       <c r="H103" t="n">
-        <v>3361.359</v>
+        <v>3380.4558</v>
       </c>
       <c r="I103" t="n">
-        <v>51.75</v>
+        <v>68.417</v>
       </c>
       <c r="J103" s="1" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="K103" t="b">
@@ -5914,16 +5914,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Raedyn Spademan</t>
+          <t>Layla Matthew</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>816647</v>
+        <v>847129</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -5959,16 +5959,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Layla Matthew</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>847129</v>
+        <v>801538</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -5976,17 +5976,17 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>3312.039</v>
+        <v>3361.359</v>
       </c>
       <c r="H105" t="n">
-        <v>3380.4558</v>
+        <v>3393.143</v>
       </c>
       <c r="I105" t="n">
-        <v>68.417</v>
+        <v>31.784</v>
       </c>
       <c r="J105" s="1" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="K105" t="b">
@@ -6004,16 +6004,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6021,17 +6021,17 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>3361.359</v>
+        <v>3380.4558</v>
       </c>
       <c r="H106" t="n">
         <v>3393.143</v>
       </c>
       <c r="I106" t="n">
-        <v>31.784</v>
+        <v>12.687</v>
       </c>
       <c r="J106" s="1" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K106" t="b">
@@ -6049,16 +6049,16 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>818654</v>
+        <v>816244</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6094,16 +6094,16 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Keira Hurry</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>816244</v>
+        <v>816275</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6111,17 +6111,17 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>3380.4558</v>
+        <v>3385.5386</v>
       </c>
       <c r="H108" t="n">
-        <v>3393.143</v>
+        <v>3600</v>
       </c>
       <c r="I108" t="n">
-        <v>12.687</v>
+        <v>214.461</v>
       </c>
       <c r="J108" s="1" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="K108" t="b">
@@ -6139,16 +6139,16 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Keira Hurry</t>
+          <t>Kate Manness</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>816275</v>
+        <v>835282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6184,16 +6184,16 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Kate Manness</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>835282</v>
+        <v>811470</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6201,17 +6201,17 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>3385.5386</v>
+        <v>3393.143</v>
       </c>
       <c r="H110" t="n">
-        <v>3600</v>
+        <v>3548.692</v>
       </c>
       <c r="I110" t="n">
-        <v>214.461</v>
+        <v>155.549</v>
       </c>
       <c r="J110" s="1" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="K110" t="b">
@@ -6229,16 +6229,16 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>811470</v>
+        <v>891409</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6249,14 +6249,14 @@
         <v>3393.143</v>
       </c>
       <c r="H111" t="n">
-        <v>3548.692</v>
+        <v>3447.7573</v>
       </c>
       <c r="I111" t="n">
-        <v>155.549</v>
+        <v>54.614</v>
       </c>
       <c r="J111" s="1" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K111" t="b">
@@ -6274,16 +6274,16 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Sara Manness</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>891409</v>
+        <v>801530</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6294,14 +6294,14 @@
         <v>3393.143</v>
       </c>
       <c r="H112" t="n">
-        <v>3447.7573</v>
+        <v>3600</v>
       </c>
       <c r="I112" t="n">
-        <v>54.614</v>
+        <v>206.857</v>
       </c>
       <c r="J112" s="1" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="K112" t="b">
@@ -6319,16 +6319,16 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sara Manness</t>
+          <t>Jessie Pellerin</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>801530</v>
+        <v>801538</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6336,17 +6336,17 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>3393.143</v>
+        <v>3447.7573</v>
       </c>
       <c r="H113" t="n">
         <v>3600</v>
       </c>
       <c r="I113" t="n">
-        <v>206.857</v>
+        <v>152.243</v>
       </c>
       <c r="J113" s="1" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K113" t="b">
@@ -6364,16 +6364,16 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Jessie Pellerin</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>801538</v>
+        <v>818654</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6384,14 +6384,14 @@
         <v>3447.7573</v>
       </c>
       <c r="H114" t="n">
-        <v>3600</v>
+        <v>3550.9062</v>
       </c>
       <c r="I114" t="n">
-        <v>152.243</v>
+        <v>103.149</v>
       </c>
       <c r="J114" s="1" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="K114" t="b">
@@ -6409,16 +6409,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Janelle Evans</t>
+          <t>Kennedy Sisson</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>818654</v>
+        <v>891409</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6426,17 +6426,17 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>3447.7573</v>
+        <v>3548.692</v>
       </c>
       <c r="H115" t="n">
-        <v>3550.9062</v>
+        <v>3594.3313</v>
       </c>
       <c r="I115" t="n">
-        <v>103.149</v>
+        <v>45.639</v>
       </c>
       <c r="J115" s="1" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="K115" t="b">
@@ -6454,16 +6454,16 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Kennedy Sisson</t>
+          <t>Isa Goettl</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>891409</v>
+        <v>816244</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6471,17 +6471,17 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>3548.692</v>
+        <v>3550.9062</v>
       </c>
       <c r="H116" t="n">
         <v>3594.3313</v>
       </c>
       <c r="I116" t="n">
-        <v>45.639</v>
+        <v>43.425</v>
       </c>
       <c r="J116" s="1" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="K116" t="b">
@@ -6499,16 +6499,16 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Isa Goettl</t>
+          <t>Manon le Scodan</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>816244</v>
+        <v>811470</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6516,17 +6516,17 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3550.9062</v>
+        <v>3594.3313</v>
       </c>
       <c r="H117" t="n">
-        <v>3594.3313</v>
+        <v>3600</v>
       </c>
       <c r="I117" t="n">
-        <v>43.425</v>
+        <v>5.669</v>
       </c>
       <c r="J117" s="1" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="K117" t="b">
@@ -6544,16 +6544,16 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Manon le Scodan</t>
+          <t>Janelle Evans</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>811470</v>
+        <v>818654</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6575,51 +6575,6 @@
         </is>
       </c>
       <c r="K118" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>CUGN</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>3</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Janelle Evans</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>818654</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>5-5</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>3594.3313</v>
-      </c>
-      <c r="H119" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I119" t="n">
-        <v>5.669</v>
-      </c>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="K119" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6799,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:22:15.568106+00:00</t>
+          <t>2026-10-03T00:23:07.074118+00:00</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6765,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16">

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:23:07.074118+00:00</t>
+          <t>2026-10-03T00:23:58.777739+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:23:58.777739+00:00</t>
+          <t>2026-10-03T00:24:49.830231+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:24:49.830231+00:00</t>
+          <t>2026-10-03T00:25:41.076006+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:25:41.076006+00:00</t>
+          <t>2026-10-03T00:26:34.189513+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:26:34.189513+00:00</t>
+          <t>2026-10-03T00:27:25.009236+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:27:25.009236+00:00</t>
+          <t>2026-10-03T00:28:16.889496+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:28:16.889496+00:00</t>
+          <t>2026-10-03T00:29:08.285599+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:29:08.285599+00:00</t>
+          <t>2026-10-03T00:29:59.558265+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:29:59.558265+00:00</t>
+          <t>2026-10-03T00:30:50.766623+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:30:50.766623+00:00</t>
+          <t>2026-10-03T00:31:42.226523+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:31:42.226523+00:00</t>
+          <t>2026-10-03T00:32:33.595564+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:32:33.595564+00:00</t>
+          <t>2026-10-03T00:33:25.676398+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:33:25.676398+00:00</t>
+          <t>2026-10-03T00:34:17.501387+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:34:17.501387+00:00</t>
+          <t>2026-10-03T00:35:08.671419+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:35:08.671419+00:00</t>
+          <t>2026-10-03T00:36:00.014412+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:36:00.014412+00:00</t>
+          <t>2026-10-03T00:36:51.188668+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:36:51.188668+00:00</t>
+          <t>2026-10-03T00:37:42.638557+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:37:42.638557+00:00</t>
+          <t>2026-10-03T00:38:34.273531+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:38:34.273531+00:00</t>
+          <t>2026-10-03T00:39:25.522863+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:39:25.522863+00:00</t>
+          <t>2026-10-03T00:40:16.771264+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:40:16.771264+00:00</t>
+          <t>2026-10-03T00:41:10.473478+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:41:10.473478+00:00</t>
+          <t>2026-10-03T00:42:01.202888+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:42:01.202888+00:00</t>
+          <t>2026-10-03T00:42:52.788656+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:42:52.788656+00:00</t>
+          <t>2026-10-03T00:43:44.472188+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:43:44.472188+00:00</t>
+          <t>2026-10-03T00:44:36.046232+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:44:36.046232+00:00</t>
+          <t>2026-10-03T00:45:27.279488+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:45:27.279488+00:00</t>
+          <t>2026-10-03T00:46:18.647170+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:46:18.647170+00:00</t>
+          <t>2026-10-03T00:47:09.957346+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:47:09.957346+00:00</t>
+          <t>2026-10-03T00:48:01.312852+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:48:01.312852+00:00</t>
+          <t>2026-10-03T00:48:52.313057+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:48:52.313057+00:00</t>
+          <t>2026-10-03T00:49:43.409772+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:49:43.409772+00:00</t>
+          <t>2026-10-03T00:50:34.576293+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:50:34.576293+00:00</t>
+          <t>2026-10-03T00:51:25.905098+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:51:25.905098+00:00</t>
+          <t>2026-10-03T00:52:17.358776+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:52:17.358776+00:00</t>
+          <t>2026-10-03T00:53:08.531475+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:53:08.531475+00:00</t>
+          <t>2026-10-03T00:53:59.352820+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:53:59.352820+00:00</t>
+          <t>2026-10-03T00:54:50.949368+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:54:50.949368+00:00</t>
+          <t>2026-10-03T00:55:42.115997+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:55:42.115997+00:00</t>
+          <t>2026-10-03T00:56:33.056789+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:56:33.056789+00:00</t>
+          <t>2026-10-03T00:57:24.395473+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:57:24.395473+00:00</t>
+          <t>2026-10-03T00:58:15.907908+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:58:15.907908+00:00</t>
+          <t>2026-10-03T00:59:07.580682+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:07.580682+00:00</t>
+          <t>2026-10-03T00:59:58.964389+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T00:59:58.964389+00:00</t>
+          <t>2026-10-03T01:00:50.077024+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:00:50.077024+00:00</t>
+          <t>2026-10-03T01:01:41.495523+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:01:41.495523+00:00</t>
+          <t>2026-10-03T01:02:32.586304+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:02:32.586304+00:00</t>
+          <t>2026-10-03T01:03:24.446362+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:03:24.446362+00:00</t>
+          <t>2026-10-03T01:04:15.410897+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:04:15.410897+00:00</t>
+          <t>2026-10-03T01:05:06.913340+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:05:06.913340+00:00</t>
+          <t>2026-10-03T01:05:58.183691+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:05:58.183691+00:00</t>
+          <t>2026-10-03T01:06:49.657622+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:06:49.657622+00:00</t>
+          <t>2026-10-03T01:07:41.386314+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:07:41.386314+00:00</t>
+          <t>2026-10-03T01:08:32.450219+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:08:32.450219+00:00</t>
+          <t>2026-10-03T01:09:23.901936+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:09:23.901936+00:00</t>
+          <t>2026-10-03T01:10:15.029593+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:10:15.029593+00:00</t>
+          <t>2026-10-03T01:11:06.272666+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:11:06.272666+00:00</t>
+          <t>2026-10-03T01:11:57.383581+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:11:57.383581+00:00</t>
+          <t>2026-10-03T01:12:48.946244+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:12:48.946244+00:00</t>
+          <t>2026-10-03T01:13:42.080812+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:13:42.080812+00:00</t>
+          <t>2026-10-03T01:14:33.194102+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:14:33.194102+00:00</t>
+          <t>2026-10-03T01:15:25.991790+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:15:25.991790+00:00</t>
+          <t>2026-10-03T01:16:18.335197+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:16:18.335197+00:00</t>
+          <t>2026-10-03T01:17:09.411303+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:17:09.411303+00:00</t>
+          <t>2026-10-03T01:18:00.616668+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:18:00.616668+00:00</t>
+          <t>2026-10-03T01:18:52.516147+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:18:52.516147+00:00</t>
+          <t>2026-10-03T01:19:43.561973+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:19:43.561973+00:00</t>
+          <t>2026-10-03T01:20:35.290198+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:20:35.290198+00:00</t>
+          <t>2026-10-03T01:21:26.557668+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:21:26.557668+00:00</t>
+          <t>2026-10-03T01:22:17.878556+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:22:17.878556+00:00</t>
+          <t>2026-10-03T01:23:08.980288+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:23:08.980288+00:00</t>
+          <t>2026-10-03T01:24:00.088275+00:00</t>
         </is>
       </c>
     </row>

--- a/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
+++ b/clarkson_intermission_toi_48d1d66f-0466-44ae-8987-278e8c64a996_p3.xlsx
@@ -6754,7 +6754,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-03T01:24:00.088275+00:00</t>
+          <t>2026-10-03T01:24:50.777812+00:00</t>
         </is>
       </c>
     </row>
